--- a/Projects/Bank Churn Excel/Bank Churn Data.xlsx
+++ b/Projects/Bank Churn Excel/Bank Churn Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\DS\tezendra\Projects\Bank Churn Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E560C77-109F-4E68-A8E2-B5590A8AA09F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EC3B08B-450C-4315-AEDB-F34768EAE14D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-109" yWindow="-109" windowWidth="26301" windowHeight="16520" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="12946" yWindow="0" windowWidth="13232" windowHeight="16397" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="2" r:id="rId7"/>
+    <pivotCache cacheId="0" r:id="rId7"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2090" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2077" uniqueCount="63">
   <si>
     <t>CustomerID</t>
   </si>
@@ -232,6 +232,9 @@
   <si>
     <t>Total</t>
   </si>
+  <si>
+    <t>Anova: Single Factor</t>
+  </si>
 </sst>
 </file>
 
@@ -280,7 +283,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -295,18 +298,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="-0.249977111117893"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.39997558519241921"/>
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -327,15 +324,6 @@
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -363,7 +351,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
@@ -402,30 +390,22 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="2" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="2" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="2" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -433,10 +413,10 @@
   </cellStyles>
   <dxfs count="2">
     <dxf>
-      <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+      <numFmt numFmtId="1" formatCode="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
+      <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -1809,6 +1789,7 @@
           </a:p>
         </c:txPr>
         <c:crossAx val="515801168"/>
+        <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
         <c:lblOffset val="100"/>
@@ -1867,6 +1848,7 @@
           </a:p>
         </c:txPr>
         <c:crossAx val="573417280"/>
+        <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:spPr>
@@ -11894,7 +11876,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{455D1343-4F52-4BE0-9764-8D777577F67E}" name="PivotTable1" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4" rowHeaderCaption="Country">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{455D1343-4F52-4BE0-9764-8D777577F67E}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4" rowHeaderCaption="Country">
   <location ref="A2:B6" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="13">
     <pivotField showAll="0"/>
@@ -11995,7 +11977,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{318F54FD-F225-4505-A6DF-850C6C3CD63E}" name="PivotTable2" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2" rowHeaderCaption="Country" colHeaderCaption="Gender">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{318F54FD-F225-4505-A6DF-850C6C3CD63E}" name="PivotTable2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2" rowHeaderCaption="Country" colHeaderCaption="Gender">
   <location ref="A2:D7" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="13">
     <pivotField showAll="0"/>
@@ -12642,14 +12624,14 @@
     <dataField name="Average of Balance" fld="7" subtotal="average" baseField="3" baseItem="0"/>
   </dataFields>
   <formats count="2">
-    <format dxfId="0">
+    <format dxfId="1">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="3" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="1">
+    <format dxfId="0">
       <pivotArea grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -12692,7 +12674,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{16744778-A184-4F77-BAC6-3631769D851D}" name="PivotTable1" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="3" rowHeaderCaption="Tenure" colHeaderCaption="Churn">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{16744778-A184-4F77-BAC6-3631769D851D}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="3" rowHeaderCaption="Tenure" colHeaderCaption="Churn">
   <location ref="A3:D16" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="13">
     <pivotField showAll="0"/>
@@ -33744,7 +33726,8 @@
   <dimension ref="A2:D7"/>
   <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="4" width="12.875" customWidth="1"/>
+    <col min="1" max="1" width="20.875" customWidth="1"/>
+    <col min="2" max="4" width="12.875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -34047,11 +34030,12 @@
     <col min="1" max="1" width="26.875" style="13" customWidth="1"/>
     <col min="2" max="2" width="31.25" style="13" customWidth="1"/>
     <col min="4" max="4" width="39.25" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="13.5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="26.5" customWidth="1"/>
+    <col min="6" max="6" width="23.875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="42.8" x14ac:dyDescent="0.25">
-      <c r="D1" s="28" t="s">
+      <c r="D1" s="18" t="s">
         <v>46</v>
       </c>
     </row>
@@ -34070,11 +34054,8 @@
       <c r="B3" s="16">
         <v>92581.54</v>
       </c>
-      <c r="D3" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="14.95" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="16">
         <v>52848.11</v>
       </c>
@@ -34089,29 +34070,16 @@
       <c r="B5" s="16">
         <v>143065.1</v>
       </c>
-      <c r="D5" s="20"/>
-      <c r="E5" s="21">
-        <v>107886.77</v>
-      </c>
-      <c r="F5" s="21">
-        <v>92581.54</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="14.95" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="16">
         <v>146739.54999999999</v>
       </c>
       <c r="B6" s="16">
         <v>125839.96</v>
-      </c>
-      <c r="D6" s="26" t="s">
-        <v>35</v>
-      </c>
-      <c r="E6" s="27">
-        <v>80343.717326868675</v>
-      </c>
-      <c r="F6" s="27">
-        <v>83394.315337263426</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -34121,14 +34089,12 @@
       <c r="B7" s="16">
         <v>58708.71</v>
       </c>
-      <c r="D7" s="18" t="s">
-        <v>36</v>
-      </c>
-      <c r="E7" s="22">
-        <v>1643613256.0054414</v>
-      </c>
-      <c r="F7" s="22">
-        <v>1724744232.4391177</v>
+      <c r="D7" s="24"/>
+      <c r="E7" s="24" t="s">
+        <v>32</v>
+      </c>
+      <c r="F7" s="24" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -34138,14 +34104,14 @@
       <c r="B8" s="16">
         <v>143532.82</v>
       </c>
-      <c r="D8" s="18" t="s">
-        <v>37</v>
-      </c>
-      <c r="E8" s="22">
-        <v>227</v>
-      </c>
-      <c r="F8" s="22">
-        <v>271</v>
+      <c r="D8" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="E8" s="25">
+        <v>80464.520189470131</v>
+      </c>
+      <c r="F8" s="25">
+        <v>83428.091898523489</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -34155,13 +34121,15 @@
       <c r="B9" s="16">
         <v>43961.45</v>
       </c>
-      <c r="D9" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="E9" s="22">
-        <v>1687777295.5963538</v>
-      </c>
-      <c r="F9" s="22"/>
+      <c r="D9" s="22" t="s">
+        <v>36</v>
+      </c>
+      <c r="E9" s="25">
+        <v>1639699948.5822766</v>
+      </c>
+      <c r="F9" s="25">
+        <v>1718690175.4343524</v>
+      </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="16">
@@ -34170,13 +34138,15 @@
       <c r="B10" s="16">
         <v>103226.64</v>
       </c>
-      <c r="D10" s="18" t="s">
-        <v>39</v>
-      </c>
-      <c r="E10" s="22">
-        <v>0</v>
-      </c>
-      <c r="F10" s="22"/>
+      <c r="D10" s="22" t="s">
+        <v>37</v>
+      </c>
+      <c r="E10" s="25">
+        <v>228</v>
+      </c>
+      <c r="F10" s="25">
+        <v>272</v>
+      </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="16">
@@ -34185,13 +34155,13 @@
       <c r="B11" s="16">
         <v>144262.57</v>
       </c>
-      <c r="D11" s="18" t="s">
-        <v>40</v>
-      </c>
-      <c r="E11" s="22">
-        <v>496</v>
-      </c>
-      <c r="F11" s="22"/>
+      <c r="D11" s="22" t="s">
+        <v>38</v>
+      </c>
+      <c r="E11" s="25">
+        <v>1682684590.1021812</v>
+      </c>
+      <c r="F11" s="25"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="16">
@@ -34200,13 +34170,13 @@
       <c r="B12" s="16">
         <v>71646.19</v>
       </c>
-      <c r="D12" s="18" t="s">
-        <v>41</v>
-      </c>
-      <c r="E12" s="22">
-        <v>-0.82529709259882889</v>
-      </c>
-      <c r="F12" s="22"/>
+      <c r="D12" s="22" t="s">
+        <v>39</v>
+      </c>
+      <c r="E12" s="25">
+        <v>0</v>
+      </c>
+      <c r="F12" s="25"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="16">
@@ -34215,13 +34185,13 @@
       <c r="B13" s="16">
         <v>130037.45</v>
       </c>
-      <c r="D13" s="18" t="s">
-        <v>42</v>
-      </c>
-      <c r="E13" s="22">
-        <v>0.20479984506155241</v>
-      </c>
-      <c r="F13" s="22"/>
+      <c r="D13" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="E13" s="25">
+        <v>498</v>
+      </c>
+      <c r="F13" s="25"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="16">
@@ -34230,13 +34200,13 @@
       <c r="B14" s="16">
         <v>137124.10999999999</v>
       </c>
-      <c r="D14" s="18" t="s">
-        <v>43</v>
-      </c>
-      <c r="E14" s="22">
-        <v>1.6479315230387441</v>
-      </c>
-      <c r="F14" s="22"/>
+      <c r="D14" s="22" t="s">
+        <v>41</v>
+      </c>
+      <c r="E14" s="25">
+        <v>-0.8046017166989673</v>
+      </c>
+      <c r="F14" s="25"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="16">
@@ -34245,73 +34215,87 @@
       <c r="B15" s="16">
         <v>107849.47</v>
       </c>
-      <c r="D15" s="24" t="s">
-        <v>44</v>
+      <c r="D15" s="22" t="s">
+        <v>42</v>
       </c>
       <c r="E15" s="25">
-        <v>0.40959969012310482</v>
-      </c>
-      <c r="F15" s="22"/>
-    </row>
-    <row r="16" spans="1:6" ht="14.95" thickBot="1" x14ac:dyDescent="0.3">
+        <v>0.21071674603755797</v>
+      </c>
+      <c r="F15" s="25"/>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="16">
         <v>129312.08</v>
       </c>
       <c r="B16" s="16">
         <v>82076.703199195108</v>
       </c>
-      <c r="D16" s="19" t="s">
-        <v>45</v>
-      </c>
-      <c r="E16" s="23">
-        <v>1.9647582832370318</v>
-      </c>
-      <c r="F16" s="23"/>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D16" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="E16" s="25">
+        <v>1.6479191388550134</v>
+      </c>
+      <c r="F16" s="25"/>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="16">
         <v>57083.95</v>
       </c>
       <c r="B17" s="16">
         <v>106833.18</v>
       </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D17" s="22" t="s">
+        <v>44</v>
+      </c>
+      <c r="E17" s="25">
+        <v>0.42143349207511593</v>
+      </c>
+      <c r="F17" s="25"/>
+    </row>
+    <row r="18" spans="1:6" ht="14.95" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="16">
         <v>129087.2</v>
       </c>
       <c r="B18" s="16">
         <v>88655.49</v>
       </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D18" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="E18" s="27">
+        <v>1.9647389829672903</v>
+      </c>
+      <c r="F18" s="27"/>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="16">
         <v>90761.77</v>
       </c>
       <c r="B19" s="16">
         <v>45305.66</v>
       </c>
-      <c r="D19" s="29"/>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D19" s="19"/>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="16">
         <v>82076.703199195108</v>
       </c>
       <c r="B20" s="16">
         <v>128936.13</v>
       </c>
-      <c r="D20" s="29"/>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D20" s="19"/>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="16">
         <v>22363.52</v>
       </c>
       <c r="B21" s="16">
         <v>39491.230000000003</v>
       </c>
-      <c r="D21" s="29"/>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D21" s="19"/>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="16">
         <v>23908.03</v>
       </c>
@@ -34319,7 +34303,7 @@
         <v>118972.35</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="16">
         <v>81519.78</v>
       </c>
@@ -34327,7 +34311,7 @@
         <v>82076.703199195108</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="16">
         <v>19803.7</v>
       </c>
@@ -34335,7 +34319,7 @@
         <v>48255.32</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="16">
         <v>124490.71</v>
       </c>
@@ -34343,7 +34327,7 @@
         <v>64920.41</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="16">
         <v>133876.07999999999</v>
       </c>
@@ -34351,7 +34335,7 @@
         <v>110877.22</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="16">
         <v>118097.5</v>
       </c>
@@ -34359,7 +34343,7 @@
         <v>21781.599999999999</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="16">
         <v>24025.919999999998</v>
       </c>
@@ -34367,7 +34351,7 @@
         <v>125168.23</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="16">
         <v>103834.77</v>
       </c>
@@ -34375,7 +34359,7 @@
         <v>40937.339999999997</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="16">
         <v>56949.24</v>
       </c>
@@ -34383,7 +34367,7 @@
         <v>29656.959999999999</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="16">
         <v>140603.54</v>
       </c>
@@ -34391,7 +34375,7 @@
         <v>16131.69</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="16">
         <v>33012.78</v>
       </c>
@@ -36254,16 +36238,15 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C579A25-9064-487F-AB78-040E4F8F7CDA}">
-  <sheetPr filterMode="1"/>
-  <dimension ref="A2:O502"/>
+  <dimension ref="A2:N502"/>
   <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.625" style="13" customWidth="1"/>
     <col min="2" max="2" width="12.25" style="13" customWidth="1"/>
-    <col min="9" max="15" width="16.625" customWidth="1"/>
+    <col min="8" max="8" width="20.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
         <v>2</v>
       </c>
@@ -36279,85 +36262,193 @@
       <c r="F2" s="14" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="3" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="H2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="4">
         <v>764</v>
       </c>
       <c r="B3" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="D3">
+      <c r="D3" s="1">
         <v>764</v>
       </c>
-    </row>
-    <row r="4" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E3" s="3">
+        <v>741</v>
+      </c>
+      <c r="F3" s="3">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" ht="14.95" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="4">
         <v>365</v>
       </c>
       <c r="B4" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="D4">
+      <c r="D4" s="1">
         <v>519</v>
       </c>
-    </row>
-    <row r="5" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E4" s="1">
+        <v>671</v>
+      </c>
+      <c r="F4" s="1">
+        <v>848</v>
+      </c>
+      <c r="H4" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="4">
         <v>519</v>
       </c>
       <c r="B5" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="D5">
+      <c r="D5" s="1">
         <v>516</v>
       </c>
-    </row>
-    <row r="6" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E5" s="3">
+        <v>519</v>
+      </c>
+      <c r="F5" s="3">
+        <v>668</v>
+      </c>
+      <c r="H5" s="24" t="s">
+        <v>48</v>
+      </c>
+      <c r="I5" s="24" t="s">
+        <v>49</v>
+      </c>
+      <c r="J5" s="24" t="s">
+        <v>50</v>
+      </c>
+      <c r="K5" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="L5" s="24" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="4">
         <v>516</v>
       </c>
       <c r="B6" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="D6">
+      <c r="D6" s="1">
         <v>432</v>
       </c>
-    </row>
-    <row r="7" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E6" s="3">
+        <v>579</v>
+      </c>
+      <c r="F6" s="3">
+        <v>797</v>
+      </c>
+      <c r="H6" s="22" t="s">
+        <v>22</v>
+      </c>
+      <c r="I6" s="22">
+        <v>157</v>
+      </c>
+      <c r="J6" s="22">
+        <v>91012</v>
+      </c>
+      <c r="K6" s="22">
+        <v>579.69426751592357</v>
+      </c>
+      <c r="L6" s="22">
+        <v>18409.213620774113</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="4">
         <v>659</v>
       </c>
       <c r="B7" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="D7">
+      <c r="D7" s="1">
         <v>570</v>
       </c>
-    </row>
-    <row r="8" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E7" s="1">
+        <v>571</v>
+      </c>
+      <c r="F7" s="1">
+        <v>738</v>
+      </c>
+      <c r="H7" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="I7" s="22">
+        <v>171</v>
+      </c>
+      <c r="J7" s="22">
+        <v>101326</v>
+      </c>
+      <c r="K7" s="22">
+        <v>592.54970760233914</v>
+      </c>
+      <c r="L7" s="22">
+        <v>19475.519573443427</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="14.95" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="4">
         <v>777</v>
       </c>
       <c r="B8" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="D8">
+      <c r="D8" s="1">
         <v>672</v>
       </c>
-    </row>
-    <row r="9" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E8" s="1">
+        <v>443</v>
+      </c>
+      <c r="F8" s="1">
+        <v>464</v>
+      </c>
+      <c r="H8" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="I8" s="23">
+        <v>172</v>
+      </c>
+      <c r="J8" s="23">
+        <v>103370</v>
+      </c>
+      <c r="K8" s="23">
+        <v>600.98837209302326</v>
+      </c>
+      <c r="L8" s="23">
+        <v>18978.912144702823</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="4">
         <v>432</v>
       </c>
       <c r="B9" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="D9">
+      <c r="D9" s="1">
         <v>698</v>
       </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="E9" s="1">
+        <v>574</v>
+      </c>
+      <c r="F9" s="1">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="4">
         <v>741</v>
       </c>
@@ -36367,38 +36458,34 @@
       <c r="D10" s="3">
         <v>684</v>
       </c>
-      <c r="E10" s="3">
-        <v>741</v>
-      </c>
-      <c r="F10" s="3">
-        <v>450</v>
-      </c>
-      <c r="I10" s="31"/>
-      <c r="J10" s="31"/>
-      <c r="K10" s="31"/>
-      <c r="L10" s="31"/>
-      <c r="M10" s="31"/>
-      <c r="N10" s="31"/>
-      <c r="O10" s="31"/>
-    </row>
-    <row r="11" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E10" s="1">
+        <v>686</v>
+      </c>
+      <c r="F10" s="1">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="14.95" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="4">
         <v>570</v>
       </c>
       <c r="B11" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="D11">
+      <c r="D11" s="1">
         <v>569</v>
       </c>
-      <c r="E11">
-        <v>671</v>
-      </c>
-      <c r="F11">
-        <v>848</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="E11" s="3">
+        <v>849</v>
+      </c>
+      <c r="F11" s="3">
+        <v>517</v>
+      </c>
+      <c r="H11" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="4">
         <v>671</v>
       </c>
@@ -36408,21 +36495,35 @@
       <c r="D12" s="3">
         <v>450</v>
       </c>
-      <c r="E12" s="3">
-        <v>519</v>
-      </c>
-      <c r="F12" s="3">
-        <v>668</v>
-      </c>
-      <c r="I12" s="31"/>
-      <c r="J12" s="31"/>
-      <c r="K12" s="31"/>
-      <c r="L12" s="31"/>
-      <c r="M12" s="31"/>
-      <c r="N12" s="31"/>
-      <c r="O12" s="31"/>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="E12" s="1">
+        <v>488</v>
+      </c>
+      <c r="F12" s="1">
+        <v>734</v>
+      </c>
+      <c r="H12" s="24" t="s">
+        <v>53</v>
+      </c>
+      <c r="I12" s="24" t="s">
+        <v>54</v>
+      </c>
+      <c r="J12" s="24" t="s">
+        <v>40</v>
+      </c>
+      <c r="K12" s="24" t="s">
+        <v>55</v>
+      </c>
+      <c r="L12" s="24" t="s">
+        <v>56</v>
+      </c>
+      <c r="M12" s="24" t="s">
+        <v>57</v>
+      </c>
+      <c r="N12" s="24" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="4">
         <v>519</v>
       </c>
@@ -36432,137 +36533,138 @@
       <c r="D13" s="3">
         <v>765</v>
       </c>
-      <c r="E13" s="3">
-        <v>579</v>
-      </c>
-      <c r="F13" s="3">
-        <v>797</v>
-      </c>
-      <c r="I13" s="31"/>
-      <c r="J13" s="31"/>
-      <c r="K13" s="31"/>
-      <c r="L13" s="31"/>
-      <c r="M13" s="31"/>
-      <c r="N13" s="31"/>
-      <c r="O13" s="31"/>
-    </row>
-    <row r="14" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E13" s="1">
+        <v>470</v>
+      </c>
+      <c r="F13" s="1">
+        <v>522</v>
+      </c>
+      <c r="H13" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="I13" s="22">
+        <v>37551.842929668725</v>
+      </c>
+      <c r="J13" s="22">
+        <v>2</v>
+      </c>
+      <c r="K13" s="22">
+        <v>18775.921464834362</v>
+      </c>
+      <c r="L13" s="25">
+        <v>0.98977132490087893</v>
+      </c>
+      <c r="M13" s="26">
+        <v>0.37239304049767863</v>
+      </c>
+      <c r="N13" s="25">
+        <v>3.0138622207623187</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="4">
         <v>672</v>
       </c>
       <c r="B14" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="D14">
+      <c r="D14" s="1">
         <v>618</v>
       </c>
-      <c r="E14">
-        <v>571</v>
-      </c>
-      <c r="F14">
-        <v>738</v>
-      </c>
-      <c r="I14" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E14" s="1">
+        <v>813</v>
+      </c>
+      <c r="F14" s="1">
+        <v>797</v>
+      </c>
+      <c r="H14" s="22" t="s">
+        <v>60</v>
+      </c>
+      <c r="I14" s="22">
+        <v>9428069.6290703285</v>
+      </c>
+      <c r="J14" s="22">
+        <v>497</v>
+      </c>
+      <c r="K14" s="22">
+        <v>18969.959012213942</v>
+      </c>
+      <c r="L14" s="22"/>
+      <c r="M14" s="22"/>
+      <c r="N14" s="22"/>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="4">
         <v>464</v>
       </c>
       <c r="B15" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="D15">
+      <c r="D15" s="1">
         <v>416</v>
       </c>
-      <c r="E15">
-        <v>443</v>
-      </c>
-      <c r="F15">
-        <v>464</v>
-      </c>
-      <c r="I15" s="20" t="s">
-        <v>48</v>
-      </c>
-      <c r="J15" s="20" t="s">
-        <v>49</v>
-      </c>
-      <c r="K15" s="20" t="s">
-        <v>50</v>
-      </c>
-      <c r="L15" s="20" t="s">
-        <v>51</v>
-      </c>
-      <c r="M15" s="20" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E15" s="1">
+        <v>694</v>
+      </c>
+      <c r="F15" s="1">
+        <v>612</v>
+      </c>
+      <c r="H15" s="22"/>
+      <c r="I15" s="22"/>
+      <c r="J15" s="22"/>
+      <c r="K15" s="22"/>
+      <c r="L15" s="22"/>
+      <c r="M15" s="22"/>
+      <c r="N15" s="22"/>
+    </row>
+    <row r="16" spans="1:14" ht="14.95" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="4">
         <v>698</v>
       </c>
       <c r="B16" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="D16">
+      <c r="D16" s="1">
         <v>462</v>
       </c>
-      <c r="E16">
-        <v>574</v>
-      </c>
-      <c r="F16">
-        <v>536</v>
-      </c>
-      <c r="I16" s="18" t="s">
-        <v>22</v>
-      </c>
-      <c r="J16" s="18">
-        <v>157</v>
-      </c>
-      <c r="K16" s="18">
-        <v>91012</v>
-      </c>
-      <c r="L16" s="18">
-        <v>579.69426751592357</v>
-      </c>
-      <c r="M16" s="18">
-        <v>18409.213620774113</v>
-      </c>
-    </row>
-    <row r="17" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E16" s="3">
+        <v>498</v>
+      </c>
+      <c r="F16" s="3">
+        <v>443</v>
+      </c>
+      <c r="H16" s="23" t="s">
+        <v>61</v>
+      </c>
+      <c r="I16" s="23">
+        <v>9465621.4719999973</v>
+      </c>
+      <c r="J16" s="23">
+        <v>499</v>
+      </c>
+      <c r="K16" s="23"/>
+      <c r="L16" s="23"/>
+      <c r="M16" s="23"/>
+      <c r="N16" s="23"/>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="4">
         <v>684</v>
       </c>
       <c r="B17" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="D17">
+      <c r="D17" s="1">
         <v>568</v>
       </c>
-      <c r="E17">
-        <v>686</v>
-      </c>
-      <c r="F17">
-        <v>452</v>
-      </c>
-      <c r="I17" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="J17" s="18">
-        <v>170</v>
-      </c>
-      <c r="K17" s="18">
-        <v>100760</v>
-      </c>
-      <c r="L17" s="18">
-        <v>592.70588235294122</v>
-      </c>
-      <c r="M17" s="18">
-        <v>19586.563870518607</v>
-      </c>
-    </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="E17" s="1">
+        <v>740</v>
+      </c>
+      <c r="F17" s="1">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="4">
         <v>579</v>
       </c>
@@ -36572,113 +36674,82 @@
       <c r="D18" s="3">
         <v>798</v>
       </c>
-      <c r="E18" s="3">
-        <v>849</v>
-      </c>
-      <c r="F18" s="3">
-        <v>517</v>
-      </c>
-      <c r="I18" s="18"/>
-      <c r="J18" s="18"/>
-      <c r="K18" s="18"/>
-      <c r="L18" s="18"/>
-      <c r="M18" s="18"/>
-      <c r="N18" s="31"/>
-      <c r="O18" s="31"/>
-    </row>
-    <row r="19" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E18" s="1">
+        <v>442</v>
+      </c>
+      <c r="F18" s="1">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="4">
         <v>569</v>
       </c>
       <c r="B19" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="D19">
+      <c r="D19" s="1">
         <v>547</v>
       </c>
-      <c r="E19">
-        <v>488</v>
-      </c>
-      <c r="F19">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="20" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E19" s="3">
+        <v>679</v>
+      </c>
+      <c r="F19" s="3">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="4">
         <v>596</v>
       </c>
       <c r="B20" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="D20">
+      <c r="D20" s="1">
         <v>694</v>
       </c>
-      <c r="E20">
-        <v>470</v>
-      </c>
-      <c r="F20">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="21" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E20" s="1">
+        <v>683</v>
+      </c>
+      <c r="F20" s="1">
+        <v>797</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="4">
         <v>450</v>
       </c>
       <c r="B21" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="D21">
+      <c r="D21" s="1">
         <v>353</v>
       </c>
-      <c r="E21">
-        <v>813</v>
-      </c>
-      <c r="F21">
-        <v>797</v>
-      </c>
-      <c r="I21" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="22" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E21" s="1">
+        <v>631</v>
+      </c>
+      <c r="F21" s="1">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="4">
         <v>765</v>
       </c>
       <c r="B22" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="D22">
+      <c r="D22" s="1">
         <v>538</v>
       </c>
-      <c r="E22">
-        <v>694</v>
-      </c>
-      <c r="F22">
-        <v>612</v>
-      </c>
-      <c r="I22" s="30" t="s">
-        <v>53</v>
-      </c>
-      <c r="J22" s="30" t="s">
-        <v>54</v>
-      </c>
-      <c r="K22" s="30" t="s">
-        <v>40</v>
-      </c>
-      <c r="L22" s="30" t="s">
-        <v>55</v>
-      </c>
-      <c r="M22" s="30" t="s">
-        <v>56</v>
-      </c>
-      <c r="N22" s="30" t="s">
-        <v>57</v>
-      </c>
-      <c r="O22" s="30" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="E22" s="1">
+        <v>469</v>
+      </c>
+      <c r="F22" s="1">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="4">
         <v>571</v>
       </c>
@@ -36689,76 +36760,47 @@
         <v>634</v>
       </c>
       <c r="E23" s="3">
-        <v>498</v>
+        <v>515</v>
       </c>
       <c r="F23" s="3">
-        <v>443</v>
-      </c>
-      <c r="I23" s="18"/>
-      <c r="J23" s="18"/>
-      <c r="K23" s="18"/>
-      <c r="L23" s="18"/>
-      <c r="M23" s="18"/>
-      <c r="N23" s="18"/>
-      <c r="O23" s="18"/>
-    </row>
-    <row r="24" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="4">
         <v>528</v>
       </c>
       <c r="B24" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="D24">
+      <c r="D24" s="1">
         <v>465</v>
       </c>
-      <c r="E24">
-        <v>740</v>
-      </c>
-      <c r="F24">
-        <v>519</v>
-      </c>
-      <c r="I24" s="18" t="s">
-        <v>60</v>
-      </c>
-      <c r="J24" s="18">
-        <v>9366851.5660172328</v>
-      </c>
-      <c r="K24" s="18">
-        <v>494</v>
-      </c>
-      <c r="L24" s="18">
-        <v>18961.237987889137</v>
-      </c>
-      <c r="M24" s="18"/>
-      <c r="N24" s="18"/>
-      <c r="O24" s="18"/>
-    </row>
-    <row r="25" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E24" s="1">
+        <v>733</v>
+      </c>
+      <c r="F24" s="1">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="4">
         <v>524</v>
       </c>
       <c r="B25" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="D25">
+      <c r="D25" s="1">
         <v>672</v>
       </c>
-      <c r="E25">
-        <v>442</v>
-      </c>
-      <c r="F25">
-        <v>392</v>
-      </c>
-      <c r="I25" s="18"/>
-      <c r="J25" s="18"/>
-      <c r="K25" s="18"/>
-      <c r="L25" s="18"/>
-      <c r="M25" s="18"/>
-      <c r="N25" s="18"/>
-      <c r="O25" s="18"/>
-    </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="E25" s="3">
+        <v>735</v>
+      </c>
+      <c r="F25" s="3">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="4">
         <v>443</v>
       </c>
@@ -36768,72 +36810,65 @@
       <c r="D26" s="3">
         <v>547</v>
       </c>
-      <c r="E26" s="3">
-        <v>679</v>
-      </c>
-      <c r="F26" s="3">
-        <v>397</v>
-      </c>
-      <c r="I26" s="18"/>
-      <c r="J26" s="18"/>
-      <c r="K26" s="18"/>
-      <c r="L26" s="18"/>
-      <c r="M26" s="18"/>
-      <c r="N26" s="18"/>
-      <c r="O26" s="18"/>
-    </row>
-    <row r="27" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E26" s="1">
+        <v>422</v>
+      </c>
+      <c r="F26" s="1">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="4">
         <v>464</v>
       </c>
       <c r="B27" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="D27">
+      <c r="D27" s="1">
         <v>532</v>
       </c>
-      <c r="E27">
-        <v>683</v>
-      </c>
-      <c r="F27">
-        <v>797</v>
-      </c>
-    </row>
-    <row r="28" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E27" s="1">
+        <v>537</v>
+      </c>
+      <c r="F27" s="1">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="4">
         <v>511</v>
       </c>
       <c r="B28" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="D28">
+      <c r="D28" s="1">
         <v>755</v>
       </c>
-      <c r="E28">
-        <v>631</v>
-      </c>
-      <c r="F28">
-        <v>746</v>
-      </c>
-    </row>
-    <row r="29" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E28" s="3">
+        <v>520</v>
+      </c>
+      <c r="F28" s="3">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="4">
         <v>618</v>
       </c>
       <c r="B29" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="D29">
+      <c r="D29" s="1">
         <v>509</v>
       </c>
-      <c r="E29">
-        <v>469</v>
-      </c>
-      <c r="F29">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="E29" s="1">
+        <v>663</v>
+      </c>
+      <c r="F29" s="1">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="4">
         <v>574</v>
       </c>
@@ -36844,37 +36879,30 @@
         <v>431</v>
       </c>
       <c r="E30" s="3">
-        <v>515</v>
+        <v>825</v>
       </c>
       <c r="F30" s="3">
-        <v>369</v>
-      </c>
-      <c r="I30" s="31"/>
-      <c r="J30" s="31"/>
-      <c r="K30" s="31"/>
-      <c r="L30" s="31"/>
-      <c r="M30" s="31"/>
-      <c r="N30" s="31"/>
-      <c r="O30" s="31"/>
-    </row>
-    <row r="31" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="4">
         <v>583</v>
       </c>
       <c r="B31" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="D31">
+      <c r="D31" s="1">
         <v>385</v>
       </c>
-      <c r="E31">
-        <v>733</v>
-      </c>
-      <c r="F31">
-        <v>430</v>
-      </c>
-    </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="E31" s="1">
+        <v>737</v>
+      </c>
+      <c r="F31" s="1">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="4">
         <v>686</v>
       </c>
@@ -36884,48 +36912,48 @@
       <c r="D32" s="3">
         <v>593</v>
       </c>
-      <c r="E32" s="3">
-        <v>735</v>
-      </c>
-      <c r="F32" s="3">
-        <v>596</v>
-      </c>
-    </row>
-    <row r="33" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E32" s="1">
+        <v>556</v>
+      </c>
+      <c r="F32" s="1">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="4">
         <v>416</v>
       </c>
       <c r="B33" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="D33">
+      <c r="D33" s="1">
         <v>604</v>
       </c>
-      <c r="E33">
-        <v>422</v>
-      </c>
-      <c r="F33">
-        <v>558</v>
-      </c>
-    </row>
-    <row r="34" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E33" s="1">
+        <v>547</v>
+      </c>
+      <c r="F33" s="1">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="4">
         <v>806</v>
       </c>
       <c r="B34" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="D34">
+      <c r="D34" s="1">
         <v>371</v>
       </c>
-      <c r="E34">
-        <v>537</v>
-      </c>
-      <c r="F34">
-        <v>739</v>
-      </c>
-    </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="E34" s="1">
+        <v>547</v>
+      </c>
+      <c r="F34" s="1">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="4">
         <v>849</v>
       </c>
@@ -36936,30 +36964,30 @@
         <v>779</v>
       </c>
       <c r="E35" s="3">
-        <v>520</v>
+        <v>700</v>
       </c>
       <c r="F35" s="3">
-        <v>579</v>
-      </c>
-    </row>
-    <row r="36" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="4">
         <v>475</v>
       </c>
       <c r="B36" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="D36">
+      <c r="D36" s="1">
         <v>844</v>
       </c>
-      <c r="E36">
-        <v>663</v>
-      </c>
-      <c r="F36">
-        <v>787</v>
-      </c>
-    </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="E36" s="1">
+        <v>514</v>
+      </c>
+      <c r="F36" s="1">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="4">
         <v>488</v>
       </c>
@@ -36969,82 +36997,82 @@
       <c r="D37" s="3">
         <v>548</v>
       </c>
-      <c r="E37" s="3">
-        <v>825</v>
-      </c>
-      <c r="F37" s="3">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="38" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E37" s="1">
+        <v>703</v>
+      </c>
+      <c r="F37" s="1">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="4">
         <v>462</v>
       </c>
       <c r="B38" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="D38">
+      <c r="D38" s="1">
         <v>424</v>
       </c>
-      <c r="E38">
-        <v>737</v>
-      </c>
-      <c r="F38">
-        <v>707</v>
-      </c>
-    </row>
-    <row r="39" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E38" s="1">
+        <v>591</v>
+      </c>
+      <c r="F38" s="1">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="4">
         <v>568</v>
       </c>
       <c r="B39" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="D39">
+      <c r="D39" s="1">
         <v>788</v>
       </c>
-      <c r="E39">
-        <v>556</v>
-      </c>
-      <c r="F39">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="40" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E39" s="1">
+        <v>585</v>
+      </c>
+      <c r="F39" s="1">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="4">
         <v>505</v>
       </c>
       <c r="B40" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="D40">
+      <c r="D40" s="1">
         <v>428</v>
       </c>
-      <c r="E40">
-        <v>547</v>
-      </c>
-      <c r="F40">
-        <v>585</v>
-      </c>
-    </row>
-    <row r="41" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E40" s="1">
+        <v>846</v>
+      </c>
+      <c r="F40" s="1">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="4">
         <v>534</v>
       </c>
       <c r="B41" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="D41">
+      <c r="D41" s="1">
         <v>483</v>
       </c>
-      <c r="E41">
-        <v>547</v>
-      </c>
-      <c r="F41">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="E41" s="3">
+        <v>477</v>
+      </c>
+      <c r="F41" s="3">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="4">
         <v>470</v>
       </c>
@@ -37054,152 +37082,99 @@
       <c r="D42" s="3">
         <v>488</v>
       </c>
-      <c r="E42" s="3">
-        <v>700</v>
-      </c>
-      <c r="F42" s="3">
-        <v>365</v>
-      </c>
-      <c r="I42" s="31"/>
-      <c r="J42" s="31"/>
-      <c r="K42" s="31"/>
-      <c r="L42" s="31"/>
-      <c r="M42" s="31"/>
-    </row>
-    <row r="43" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E42" s="1">
+        <v>362</v>
+      </c>
+      <c r="F42" s="1">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="4">
         <v>671</v>
       </c>
       <c r="B43" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="D43">
+      <c r="D43" s="1">
         <v>688</v>
       </c>
-      <c r="E43">
-        <v>514</v>
-      </c>
-      <c r="F43">
-        <v>499</v>
-      </c>
-    </row>
-    <row r="44" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E43" s="1">
+        <v>468</v>
+      </c>
+      <c r="F43" s="1">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="4">
         <v>798</v>
       </c>
       <c r="B44" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="D44">
+      <c r="D44" s="1">
         <v>367</v>
       </c>
-      <c r="E44">
-        <v>703</v>
-      </c>
-      <c r="F44">
-        <v>561</v>
-      </c>
-      <c r="I44" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="45" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E44" s="1">
+        <v>724</v>
+      </c>
+      <c r="F44" s="1">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="4">
         <v>547</v>
       </c>
       <c r="B45" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="D45">
+      <c r="D45" s="1">
         <v>502</v>
       </c>
-      <c r="E45">
-        <v>591</v>
-      </c>
-      <c r="F45">
-        <v>682</v>
-      </c>
-      <c r="I45" s="20" t="s">
-        <v>48</v>
-      </c>
-      <c r="J45" s="20" t="s">
-        <v>49</v>
-      </c>
-      <c r="K45" s="20" t="s">
-        <v>50</v>
-      </c>
-      <c r="L45" s="20" t="s">
-        <v>51</v>
-      </c>
-      <c r="M45" s="20" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="46" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E45" s="1">
+        <v>465</v>
+      </c>
+      <c r="F45" s="1">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="4">
         <v>694</v>
       </c>
       <c r="B46" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="D46">
+      <c r="D46" s="1">
         <v>675</v>
       </c>
-      <c r="E46">
-        <v>585</v>
-      </c>
-      <c r="F46">
-        <v>634</v>
-      </c>
-      <c r="I46" s="18" t="s">
-        <v>22</v>
-      </c>
-      <c r="J46" s="18">
-        <v>157</v>
-      </c>
-      <c r="K46" s="18">
-        <v>91012</v>
-      </c>
-      <c r="L46" s="18">
-        <v>579.69426751592357</v>
-      </c>
-      <c r="M46" s="18">
-        <v>18409.213620774113</v>
-      </c>
-    </row>
-    <row r="47" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E46" s="1">
+        <v>759</v>
+      </c>
+      <c r="F46" s="1">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="4">
         <v>640</v>
       </c>
       <c r="B47" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="D47">
+      <c r="D47" s="1">
         <v>527</v>
       </c>
-      <c r="E47">
-        <v>846</v>
-      </c>
-      <c r="F47">
-        <v>716</v>
-      </c>
-      <c r="I47" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="J47" s="18">
-        <v>170</v>
-      </c>
-      <c r="K47" s="18">
-        <v>100760</v>
-      </c>
-      <c r="L47" s="18">
-        <v>592.70588235294122</v>
-      </c>
-      <c r="M47" s="18">
-        <v>19586.563870518607</v>
-      </c>
-    </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="E47" s="1">
+        <v>848</v>
+      </c>
+      <c r="F47" s="1">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="4">
         <v>813</v>
       </c>
@@ -37210,177 +37185,115 @@
         <v>502</v>
       </c>
       <c r="E48" s="3">
-        <v>477</v>
+        <v>460</v>
       </c>
       <c r="F48" s="3">
-        <v>528</v>
-      </c>
-      <c r="I48" s="18"/>
-      <c r="J48" s="18"/>
-      <c r="K48" s="18"/>
-      <c r="L48" s="18"/>
-      <c r="M48" s="18"/>
-    </row>
-    <row r="49" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="4">
         <v>353</v>
       </c>
       <c r="B49" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="D49">
+      <c r="D49" s="1">
         <v>752</v>
       </c>
-      <c r="E49">
-        <v>362</v>
-      </c>
-      <c r="F49">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="50" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E49" s="1">
+        <v>414</v>
+      </c>
+      <c r="F49" s="1">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="4">
         <v>538</v>
       </c>
       <c r="B50" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="D50">
+      <c r="D50" s="1">
         <v>396</v>
       </c>
-      <c r="E50">
-        <v>468</v>
-      </c>
-      <c r="F50">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="51" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E50" s="3">
+        <v>423</v>
+      </c>
+      <c r="F50" s="3">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="4">
         <v>588</v>
       </c>
       <c r="B51" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="D51">
+      <c r="D51" s="1">
         <v>687</v>
       </c>
-      <c r="E51">
-        <v>724</v>
-      </c>
-      <c r="F51">
-        <v>493</v>
-      </c>
-      <c r="I51" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="52" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E51" s="3">
+        <v>398</v>
+      </c>
+      <c r="F51" s="3">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="4">
         <v>515</v>
       </c>
       <c r="B52" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="D52">
+      <c r="D52" s="1">
         <v>507</v>
       </c>
-      <c r="E52">
-        <v>465</v>
-      </c>
-      <c r="F52">
-        <v>505</v>
-      </c>
-      <c r="I52" t="s">
-        <v>53</v>
-      </c>
-      <c r="J52" t="s">
-        <v>54</v>
-      </c>
-      <c r="K52" t="s">
-        <v>40</v>
-      </c>
-      <c r="L52" t="s">
-        <v>55</v>
-      </c>
-      <c r="M52" t="s">
-        <v>56</v>
-      </c>
-      <c r="N52" t="s">
-        <v>57</v>
-      </c>
-      <c r="O52" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="53" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E52" s="1">
+        <v>426</v>
+      </c>
+      <c r="F52" s="1">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="4">
         <v>521</v>
       </c>
       <c r="B53" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="D53">
+      <c r="D53" s="1">
         <v>652</v>
       </c>
-      <c r="E53">
-        <v>759</v>
-      </c>
-      <c r="F53">
-        <v>702</v>
-      </c>
-      <c r="I53" t="s">
-        <v>59</v>
-      </c>
-      <c r="J53">
-        <v>44357.34746366553</v>
-      </c>
-      <c r="K53">
-        <v>2</v>
-      </c>
-      <c r="L53">
-        <v>22178.673731832765</v>
-      </c>
-      <c r="M53">
-        <v>1.1696848985281794</v>
-      </c>
-      <c r="N53">
-        <v>0.31132308392705554</v>
-      </c>
-      <c r="O53">
-        <v>3.0139727676779984</v>
-      </c>
-    </row>
-    <row r="54" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E53" s="1">
+        <v>843</v>
+      </c>
+      <c r="F53" s="1">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="4">
         <v>561</v>
       </c>
       <c r="B54" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="D54">
+      <c r="D54" s="1">
         <v>474</v>
       </c>
-      <c r="E54">
-        <v>848</v>
-      </c>
-      <c r="F54">
-        <v>835</v>
-      </c>
-      <c r="I54" t="s">
-        <v>60</v>
-      </c>
-      <c r="J54">
-        <v>9366851.5660172328</v>
-      </c>
-      <c r="K54">
-        <v>494</v>
-      </c>
-      <c r="L54">
-        <v>18961.237987889137</v>
-      </c>
-    </row>
-    <row r="55" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="E54" s="1">
+        <v>398</v>
+      </c>
+      <c r="F54" s="1">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="4">
         <v>694</v>
       </c>
@@ -37390,45 +37303,31 @@
       <c r="D55" s="3">
         <v>713</v>
       </c>
-      <c r="E55" s="3">
-        <v>460</v>
-      </c>
-      <c r="F55" s="3">
-        <v>459</v>
-      </c>
-      <c r="I55" s="31"/>
-      <c r="J55" s="31"/>
-      <c r="K55" s="31"/>
-      <c r="L55" s="31"/>
-      <c r="M55" s="31"/>
-    </row>
-    <row r="56" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E55" s="1">
+        <v>421</v>
+      </c>
+      <c r="F55" s="1">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="4">
         <v>420</v>
       </c>
       <c r="B56" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="D56">
+      <c r="D56" s="1">
         <v>839</v>
       </c>
-      <c r="E56">
-        <v>414</v>
-      </c>
-      <c r="F56">
-        <v>750</v>
-      </c>
-      <c r="I56" t="s">
-        <v>61</v>
-      </c>
-      <c r="J56">
-        <v>9411208.9134808984</v>
-      </c>
-      <c r="K56">
-        <v>496</v>
-      </c>
-    </row>
-    <row r="57" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="E56" s="3">
+        <v>696</v>
+      </c>
+      <c r="F56" s="3">
+        <v>789</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="4">
         <v>498</v>
       </c>
@@ -37438,19 +37337,14 @@
       <c r="D57" s="3">
         <v>724</v>
       </c>
-      <c r="E57" s="3">
-        <v>423</v>
-      </c>
-      <c r="F57" s="3">
-        <v>694</v>
-      </c>
-      <c r="I57" s="31"/>
-      <c r="J57" s="31"/>
-      <c r="K57" s="31"/>
-      <c r="L57" s="31"/>
-      <c r="M57" s="31"/>
-    </row>
-    <row r="58" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="E57" s="1">
+        <v>844</v>
+      </c>
+      <c r="F57" s="1">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="4">
         <v>740</v>
       </c>
@@ -37460,87 +37354,82 @@
       <c r="D58" s="3">
         <v>496</v>
       </c>
-      <c r="E58" s="3">
-        <v>398</v>
-      </c>
-      <c r="F58" s="3">
-        <v>490</v>
-      </c>
-      <c r="I58" s="31"/>
-      <c r="J58" s="31"/>
-      <c r="K58" s="31"/>
-      <c r="L58" s="31"/>
-      <c r="M58" s="31"/>
-    </row>
-    <row r="59" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E58" s="1">
+        <v>725</v>
+      </c>
+      <c r="F58" s="1">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="4">
         <v>634</v>
       </c>
       <c r="B59" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="D59">
+      <c r="D59" s="1">
         <v>610</v>
       </c>
-      <c r="E59">
-        <v>426</v>
-      </c>
-      <c r="F59">
-        <v>739</v>
-      </c>
-    </row>
-    <row r="60" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E59" s="1">
+        <v>370</v>
+      </c>
+      <c r="F59" s="1">
+        <v>814</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="4">
         <v>465</v>
       </c>
       <c r="B60" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="D60">
+      <c r="D60" s="1">
         <v>481</v>
       </c>
-      <c r="E60">
-        <v>843</v>
-      </c>
-      <c r="F60">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="61" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E60" s="1">
+        <v>760</v>
+      </c>
+      <c r="F60" s="1">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="4">
         <v>740</v>
       </c>
       <c r="B61" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="D61">
+      <c r="D61" s="1">
         <v>466</v>
       </c>
-      <c r="E61">
-        <v>398</v>
-      </c>
-      <c r="F61">
-        <v>512</v>
-      </c>
-    </row>
-    <row r="62" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E61" s="1">
+        <v>654</v>
+      </c>
+      <c r="F61" s="1">
+        <v>812</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="4">
         <v>672</v>
       </c>
       <c r="B62" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="D62">
+      <c r="D62" s="1">
         <v>816</v>
       </c>
-      <c r="E62">
-        <v>421</v>
-      </c>
-      <c r="F62">
-        <v>695</v>
-      </c>
-    </row>
-    <row r="63" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="E62" s="1">
+        <v>615</v>
+      </c>
+      <c r="F62" s="1">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="4">
         <v>442</v>
       </c>
@@ -37551,112 +37440,112 @@
         <v>529</v>
       </c>
       <c r="E63" s="3">
-        <v>696</v>
+        <v>722</v>
       </c>
       <c r="F63" s="3">
-        <v>789</v>
-      </c>
-    </row>
-    <row r="64" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+        <v>774</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="4">
         <v>826</v>
       </c>
       <c r="B64" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="D64">
+      <c r="D64" s="1">
         <v>399</v>
       </c>
-      <c r="E64">
-        <v>844</v>
-      </c>
-      <c r="F64">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E64" s="1">
+        <v>583</v>
+      </c>
+      <c r="F64" s="1">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="4">
         <v>452</v>
       </c>
       <c r="B65" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="D65">
+      <c r="D65" s="1">
         <v>424</v>
       </c>
-      <c r="E65">
-        <v>725</v>
-      </c>
-      <c r="F65">
-        <v>503</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E65" s="1">
+        <v>450</v>
+      </c>
+      <c r="F65" s="1">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="4">
         <v>707</v>
       </c>
       <c r="B66" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="D66">
+      <c r="D66" s="1">
         <v>840</v>
       </c>
-      <c r="E66">
-        <v>370</v>
-      </c>
-      <c r="F66">
+      <c r="E66" s="3">
+        <v>454</v>
+      </c>
+      <c r="F66" s="3">
         <v>814</v>
       </c>
     </row>
-    <row r="67" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="4">
         <v>729</v>
       </c>
       <c r="B67" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="D67">
+      <c r="D67" s="1">
         <v>671</v>
       </c>
-      <c r="E67">
-        <v>760</v>
-      </c>
-      <c r="F67">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E67" s="1">
+        <v>771</v>
+      </c>
+      <c r="F67" s="1">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" s="4">
         <v>547</v>
       </c>
       <c r="B68" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="D68">
+      <c r="D68" s="1">
         <v>530</v>
       </c>
-      <c r="E68">
-        <v>654</v>
-      </c>
-      <c r="F68">
-        <v>812</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E68" s="1">
+        <v>728</v>
+      </c>
+      <c r="F68" s="1">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" s="4">
         <v>459</v>
       </c>
       <c r="B69" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="D69">
+      <c r="D69" s="1">
         <v>800</v>
       </c>
-      <c r="E69">
-        <v>615</v>
-      </c>
-      <c r="F69">
-        <v>613</v>
+      <c r="E69" s="1">
+        <v>760</v>
+      </c>
+      <c r="F69" s="1">
+        <v>729</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
@@ -37669,45 +37558,45 @@
       <c r="D70" s="3">
         <v>608</v>
       </c>
-      <c r="E70" s="3">
-        <v>722</v>
-      </c>
-      <c r="F70" s="3">
-        <v>774</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E70" s="1">
+        <v>422</v>
+      </c>
+      <c r="F70" s="1">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" s="4">
         <v>450</v>
       </c>
       <c r="B71" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="D71">
+      <c r="D71" s="1">
         <v>714</v>
       </c>
-      <c r="E71">
+      <c r="E71" s="1">
+        <v>624</v>
+      </c>
+      <c r="F71" s="1">
         <v>583</v>
       </c>
-      <c r="F71">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="4">
         <v>532</v>
       </c>
       <c r="B72" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="D72">
+      <c r="D72" s="1">
         <v>695</v>
       </c>
-      <c r="E72">
-        <v>450</v>
-      </c>
-      <c r="F72">
-        <v>452</v>
+      <c r="E72" s="1">
+        <v>758</v>
+      </c>
+      <c r="F72" s="1">
+        <v>408</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
@@ -37720,164 +37609,164 @@
       <c r="D73" s="3">
         <v>730</v>
       </c>
-      <c r="E73" s="3">
-        <v>454</v>
-      </c>
-      <c r="F73" s="3">
-        <v>814</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E73" s="1">
+        <v>389</v>
+      </c>
+      <c r="F73" s="1">
+        <v>772</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" s="4">
         <v>755</v>
       </c>
       <c r="B74" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="D74">
+      <c r="D74" s="1">
         <v>723</v>
       </c>
-      <c r="E74">
-        <v>771</v>
-      </c>
-      <c r="F74">
-        <v>642</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E74" s="1">
+        <v>473</v>
+      </c>
+      <c r="F74" s="1">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" s="4">
         <v>509</v>
       </c>
       <c r="B75" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="D75">
+      <c r="D75" s="1">
         <v>440</v>
       </c>
-      <c r="E75">
-        <v>728</v>
-      </c>
-      <c r="F75">
-        <v>696</v>
-      </c>
-    </row>
-    <row r="76" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E75" s="1">
+        <v>545</v>
+      </c>
+      <c r="F75" s="1">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="4">
         <v>431</v>
       </c>
       <c r="B76" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="D76">
+      <c r="D76" s="1">
         <v>418</v>
       </c>
-      <c r="E76">
-        <v>760</v>
-      </c>
-      <c r="F76">
-        <v>729</v>
-      </c>
-    </row>
-    <row r="77" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E76" s="3">
+        <v>488</v>
+      </c>
+      <c r="F76" s="3">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" s="4">
         <v>385</v>
       </c>
       <c r="B77" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="D77">
+      <c r="D77" s="1">
         <v>360</v>
       </c>
-      <c r="E77">
-        <v>422</v>
-      </c>
-      <c r="F77">
-        <v>735</v>
-      </c>
-    </row>
-    <row r="78" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E77" s="1">
+        <v>740</v>
+      </c>
+      <c r="F77" s="1">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" s="4">
         <v>587</v>
       </c>
       <c r="B78" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="D78">
+      <c r="D78" s="1">
         <v>575</v>
       </c>
-      <c r="E78">
-        <v>624</v>
-      </c>
-      <c r="F78">
-        <v>583</v>
-      </c>
-    </row>
-    <row r="79" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E78" s="1">
+        <v>791</v>
+      </c>
+      <c r="F78" s="1">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" s="4">
         <v>593</v>
       </c>
       <c r="B79" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="D79">
+      <c r="D79" s="1">
         <v>639</v>
       </c>
-      <c r="E79">
-        <v>758</v>
-      </c>
-      <c r="F79">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="80" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E79" s="1">
+        <v>753</v>
+      </c>
+      <c r="F79" s="1">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" s="4">
         <v>600</v>
       </c>
       <c r="B80" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="D80">
+      <c r="D80" s="1">
         <v>656</v>
       </c>
-      <c r="E80">
-        <v>389</v>
-      </c>
-      <c r="F80">
-        <v>772</v>
-      </c>
-    </row>
-    <row r="81" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E80" s="1">
+        <v>468</v>
+      </c>
+      <c r="F80" s="1">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" s="4">
         <v>742</v>
       </c>
       <c r="B81" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="D81">
+      <c r="D81" s="1">
         <v>560</v>
       </c>
-      <c r="E81">
-        <v>473</v>
-      </c>
-      <c r="F81">
-        <v>485</v>
-      </c>
-    </row>
-    <row r="82" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E81" s="1">
+        <v>478</v>
+      </c>
+      <c r="F81" s="1">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" s="4">
         <v>604</v>
       </c>
       <c r="B82" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="D82">
+      <c r="D82" s="1">
         <v>626</v>
       </c>
-      <c r="E82">
-        <v>545</v>
-      </c>
-      <c r="F82">
-        <v>640</v>
+      <c r="E82" s="1">
+        <v>715</v>
+      </c>
+      <c r="F82" s="1">
+        <v>596</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
@@ -37890,130 +37779,130 @@
       <c r="D83" s="3">
         <v>572</v>
       </c>
-      <c r="E83" s="3">
-        <v>488</v>
-      </c>
-      <c r="F83" s="3">
-        <v>521</v>
-      </c>
-    </row>
-    <row r="84" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E83" s="1">
+        <v>621</v>
+      </c>
+      <c r="F83" s="1">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" s="4">
         <v>371</v>
       </c>
       <c r="B84" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="D84">
+      <c r="D84" s="1">
         <v>502</v>
       </c>
-      <c r="E84">
-        <v>740</v>
-      </c>
-      <c r="F84">
-        <v>550</v>
-      </c>
-    </row>
-    <row r="85" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E84" s="3">
+        <v>468</v>
+      </c>
+      <c r="F84" s="3">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" s="4">
         <v>779</v>
       </c>
       <c r="B85" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="D85">
+      <c r="D85" s="1">
         <v>496</v>
       </c>
-      <c r="E85">
-        <v>791</v>
-      </c>
-      <c r="F85">
-        <v>742</v>
-      </c>
-    </row>
-    <row r="86" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E85" s="3">
+        <v>383</v>
+      </c>
+      <c r="F85" s="3">
+        <v>751</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" s="4">
         <v>579</v>
       </c>
       <c r="B86" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="D86">
+      <c r="D86" s="1">
         <v>561</v>
       </c>
-      <c r="E86">
-        <v>753</v>
-      </c>
-      <c r="F86">
-        <v>777</v>
-      </c>
-    </row>
-    <row r="87" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E86" s="3">
+        <v>501</v>
+      </c>
+      <c r="F86" s="3">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" s="4">
         <v>820</v>
       </c>
       <c r="B87" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="D87">
+      <c r="D87" s="1">
         <v>545</v>
       </c>
-      <c r="E87">
-        <v>468</v>
-      </c>
-      <c r="F87">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="88" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E87" s="3">
+        <v>746</v>
+      </c>
+      <c r="F87" s="3">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" s="4">
         <v>750</v>
       </c>
       <c r="B88" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="D88">
+      <c r="D88" s="1">
         <v>705</v>
       </c>
-      <c r="E88">
-        <v>478</v>
-      </c>
-      <c r="F88">
-        <v>588</v>
-      </c>
-    </row>
-    <row r="89" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E88" s="1">
+        <v>739</v>
+      </c>
+      <c r="F88" s="1">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" s="4">
         <v>503</v>
       </c>
       <c r="B89" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="D89">
+      <c r="D89" s="1">
         <v>804</v>
       </c>
-      <c r="E89">
-        <v>715</v>
-      </c>
-      <c r="F89">
-        <v>596</v>
-      </c>
-    </row>
-    <row r="90" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E89" s="1">
+        <v>388</v>
+      </c>
+      <c r="F89" s="1">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" s="4">
         <v>844</v>
       </c>
       <c r="B90" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="D90">
+      <c r="D90" s="1">
         <v>400</v>
       </c>
-      <c r="E90">
-        <v>621</v>
-      </c>
-      <c r="F90">
-        <v>506</v>
+      <c r="E90" s="1">
+        <v>616</v>
+      </c>
+      <c r="F90" s="1">
+        <v>767</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
@@ -38026,11 +37915,11 @@
       <c r="D91" s="3">
         <v>370</v>
       </c>
-      <c r="E91" s="3">
-        <v>468</v>
-      </c>
-      <c r="F91" s="3">
-        <v>681</v>
+      <c r="E91" s="1">
+        <v>356</v>
+      </c>
+      <c r="F91" s="1">
+        <v>455</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
@@ -38043,11 +37932,11 @@
       <c r="D92" s="3">
         <v>521</v>
       </c>
-      <c r="E92" s="3">
-        <v>383</v>
-      </c>
-      <c r="F92" s="3">
-        <v>751</v>
+      <c r="E92" s="1">
+        <v>731</v>
+      </c>
+      <c r="F92" s="1">
+        <v>651</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
@@ -38060,11 +37949,11 @@
       <c r="D93" s="3">
         <v>455</v>
       </c>
-      <c r="E93" s="3">
-        <v>501</v>
-      </c>
-      <c r="F93" s="3">
-        <v>437</v>
+      <c r="E93" s="1">
+        <v>452</v>
+      </c>
+      <c r="F93" s="1">
+        <v>635</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
@@ -38077,147 +37966,147 @@
       <c r="D94" s="3">
         <v>544</v>
       </c>
-      <c r="E94" s="3">
-        <v>746</v>
-      </c>
-      <c r="F94" s="3">
-        <v>718</v>
-      </c>
-    </row>
-    <row r="95" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E94" s="1">
+        <v>732</v>
+      </c>
+      <c r="F94" s="1">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" s="4">
         <v>739</v>
       </c>
       <c r="B95" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="D95">
+      <c r="D95" s="1">
         <v>575</v>
       </c>
-      <c r="E95">
-        <v>739</v>
-      </c>
-      <c r="F95">
-        <v>744</v>
-      </c>
-    </row>
-    <row r="96" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E95" s="1">
+        <v>528</v>
+      </c>
+      <c r="F95" s="1">
+        <v>760</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" s="4">
         <v>548</v>
       </c>
       <c r="B96" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="D96">
+      <c r="D96" s="1">
         <v>691</v>
       </c>
-      <c r="E96">
-        <v>388</v>
-      </c>
-      <c r="F96">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="97" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E96" s="3">
+        <v>682</v>
+      </c>
+      <c r="F96" s="3">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" s="4">
         <v>746</v>
       </c>
       <c r="B97" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="D97">
+      <c r="D97" s="1">
         <v>720</v>
       </c>
-      <c r="E97">
-        <v>616</v>
-      </c>
-      <c r="F97">
-        <v>767</v>
-      </c>
-    </row>
-    <row r="98" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E97" s="1">
+        <v>507</v>
+      </c>
+      <c r="F97" s="1">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" s="4">
         <v>696</v>
       </c>
       <c r="B98" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="D98">
+      <c r="D98" s="1">
         <v>739</v>
       </c>
-      <c r="E98">
-        <v>356</v>
-      </c>
-      <c r="F98">
-        <v>455</v>
-      </c>
-    </row>
-    <row r="99" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E98" s="1">
+        <v>465</v>
+      </c>
+      <c r="F98" s="1">
+        <v>842</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" s="4">
         <v>424</v>
       </c>
       <c r="B99" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="D99">
+      <c r="D99" s="1">
         <v>531</v>
       </c>
-      <c r="E99">
-        <v>731</v>
-      </c>
-      <c r="F99">
-        <v>651</v>
-      </c>
-    </row>
-    <row r="100" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E99" s="1">
+        <v>806</v>
+      </c>
+      <c r="F99" s="1">
+        <v>806</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" s="4">
         <v>788</v>
       </c>
       <c r="B100" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="D100">
+      <c r="D100" s="1">
         <v>543</v>
       </c>
-      <c r="E100">
-        <v>452</v>
-      </c>
-      <c r="F100">
-        <v>635</v>
-      </c>
-    </row>
-    <row r="101" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E100" s="1">
+        <v>649</v>
+      </c>
+      <c r="F100" s="1">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" s="4">
         <v>428</v>
       </c>
       <c r="B101" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="D101">
+      <c r="D101" s="1">
         <v>426</v>
       </c>
-      <c r="E101">
-        <v>732</v>
-      </c>
-      <c r="F101">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="102" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E101" s="3">
+        <v>429</v>
+      </c>
+      <c r="F101" s="3">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" s="4">
         <v>668</v>
       </c>
       <c r="B102" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="D102">
+      <c r="D102" s="1">
         <v>363</v>
       </c>
-      <c r="E102">
-        <v>528</v>
-      </c>
-      <c r="F102">
-        <v>760</v>
+      <c r="E102" s="3">
+        <v>470</v>
+      </c>
+      <c r="F102" s="3">
+        <v>433</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
@@ -38230,79 +38119,79 @@
       <c r="D103" s="3">
         <v>586</v>
       </c>
-      <c r="E103" s="3">
-        <v>682</v>
-      </c>
-      <c r="F103" s="3">
-        <v>718</v>
-      </c>
-    </row>
-    <row r="104" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E103" s="1">
+        <v>695</v>
+      </c>
+      <c r="F103" s="1">
+        <v>821</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" s="4">
         <v>549</v>
       </c>
       <c r="B104" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="D104">
+      <c r="D104" s="1">
         <v>563</v>
       </c>
-      <c r="E104">
-        <v>507</v>
-      </c>
-      <c r="F104">
-        <v>651</v>
-      </c>
-    </row>
-    <row r="105" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E104" s="1">
+        <v>572</v>
+      </c>
+      <c r="F104" s="1">
+        <v>801</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" s="4">
         <v>651</v>
       </c>
       <c r="B105" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="D105">
+      <c r="D105" s="1">
         <v>356</v>
       </c>
-      <c r="E105">
-        <v>465</v>
-      </c>
-      <c r="F105">
-        <v>842</v>
-      </c>
-    </row>
-    <row r="106" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E105" s="1">
+        <v>442</v>
+      </c>
+      <c r="F105" s="1">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" s="4">
         <v>483</v>
       </c>
       <c r="B106" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="D106">
+      <c r="D106" s="1">
         <v>450</v>
       </c>
-      <c r="E106">
-        <v>806</v>
-      </c>
-      <c r="F106">
-        <v>806</v>
-      </c>
-    </row>
-    <row r="107" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E106" s="3">
+        <v>455</v>
+      </c>
+      <c r="F106" s="3">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" s="4">
         <v>397</v>
       </c>
       <c r="B107" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="D107">
+      <c r="D107" s="1">
         <v>390</v>
       </c>
-      <c r="E107">
-        <v>649</v>
-      </c>
-      <c r="F107">
-        <v>584</v>
+      <c r="E107" s="3">
+        <v>398</v>
+      </c>
+      <c r="F107" s="3">
+        <v>515</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
@@ -38315,11 +38204,11 @@
       <c r="D108" s="3">
         <v>409</v>
       </c>
-      <c r="E108" s="3">
-        <v>429</v>
-      </c>
-      <c r="F108" s="3">
-        <v>524</v>
+      <c r="E108" s="1">
+        <v>508</v>
+      </c>
+      <c r="F108" s="1">
+        <v>390</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
@@ -38333,61 +38222,61 @@
         <v>846</v>
       </c>
       <c r="E109" s="3">
-        <v>470</v>
+        <v>739</v>
       </c>
       <c r="F109" s="3">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="110" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+        <v>834</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" s="4">
         <v>801</v>
       </c>
       <c r="B110" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="D110">
+      <c r="D110" s="1">
         <v>558</v>
       </c>
-      <c r="E110">
-        <v>695</v>
-      </c>
-      <c r="F110">
-        <v>821</v>
-      </c>
-    </row>
-    <row r="111" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E110" s="1">
+        <v>463</v>
+      </c>
+      <c r="F110" s="1">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" s="4">
         <v>488</v>
       </c>
       <c r="B111" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="D111">
+      <c r="D111" s="1">
         <v>443</v>
       </c>
-      <c r="E111">
-        <v>572</v>
-      </c>
-      <c r="F111">
-        <v>801</v>
-      </c>
-    </row>
-    <row r="112" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E111" s="3">
+        <v>445</v>
+      </c>
+      <c r="F111" s="3">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" s="4">
         <v>592</v>
       </c>
       <c r="B112" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="D112">
+      <c r="D112" s="1">
         <v>763</v>
       </c>
-      <c r="E112">
-        <v>442</v>
-      </c>
-      <c r="F112">
-        <v>587</v>
+      <c r="E112" s="1">
+        <v>670</v>
+      </c>
+      <c r="F112" s="1">
+        <v>624</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
@@ -38401,10 +38290,10 @@
         <v>753</v>
       </c>
       <c r="E113" s="3">
-        <v>455</v>
+        <v>696</v>
       </c>
       <c r="F113" s="3">
-        <v>511</v>
+        <v>660</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
@@ -38417,28 +38306,28 @@
       <c r="D114" s="3">
         <v>433</v>
       </c>
-      <c r="E114" s="3">
-        <v>398</v>
-      </c>
-      <c r="F114" s="3">
-        <v>515</v>
-      </c>
-    </row>
-    <row r="115" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E114" s="1">
+        <v>837</v>
+      </c>
+      <c r="F114" s="1">
+        <v>801</v>
+      </c>
+    </row>
+    <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" s="4">
         <v>695</v>
       </c>
       <c r="B115" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="D115">
+      <c r="D115" s="1">
         <v>477</v>
       </c>
-      <c r="E115">
-        <v>508</v>
-      </c>
-      <c r="F115">
-        <v>390</v>
+      <c r="E115" s="1">
+        <v>500</v>
+      </c>
+      <c r="F115" s="1">
+        <v>746</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
@@ -38451,28 +38340,28 @@
       <c r="D116" s="3">
         <v>611</v>
       </c>
-      <c r="E116" s="3">
-        <v>739</v>
-      </c>
-      <c r="F116" s="3">
+      <c r="E116" s="1">
         <v>834</v>
       </c>
-    </row>
-    <row r="117" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="F116" s="1">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" s="4">
         <v>475</v>
       </c>
       <c r="B117" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="D117">
+      <c r="D117" s="1">
         <v>810</v>
       </c>
-      <c r="E117">
-        <v>463</v>
-      </c>
-      <c r="F117">
-        <v>708</v>
+      <c r="E117" s="3">
+        <v>698</v>
+      </c>
+      <c r="F117" s="3">
+        <v>607</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
@@ -38485,28 +38374,28 @@
       <c r="D118" s="3">
         <v>746</v>
       </c>
-      <c r="E118" s="3">
-        <v>445</v>
-      </c>
-      <c r="F118" s="3">
-        <v>682</v>
-      </c>
-    </row>
-    <row r="119" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E118" s="1">
+        <v>836</v>
+      </c>
+      <c r="F118" s="1">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" s="4">
         <v>688</v>
       </c>
       <c r="B119" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="D119">
+      <c r="D119" s="1">
         <v>350</v>
       </c>
-      <c r="E119">
-        <v>670</v>
-      </c>
-      <c r="F119">
-        <v>624</v>
+      <c r="E119" s="3">
+        <v>530</v>
+      </c>
+      <c r="F119" s="3">
+        <v>412</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
@@ -38519,62 +38408,62 @@
       <c r="D120" s="3">
         <v>565</v>
       </c>
-      <c r="E120" s="3">
-        <v>696</v>
-      </c>
-      <c r="F120" s="3">
-        <v>660</v>
-      </c>
-    </row>
-    <row r="121" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E120" s="1">
+        <v>763</v>
+      </c>
+      <c r="F120" s="1">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" s="4">
         <v>536</v>
       </c>
       <c r="B121" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="D121">
+      <c r="D121" s="1">
         <v>680</v>
       </c>
-      <c r="E121">
-        <v>837</v>
-      </c>
-      <c r="F121">
-        <v>801</v>
-      </c>
-    </row>
-    <row r="122" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E121" s="1">
+        <v>557</v>
+      </c>
+      <c r="F121" s="1">
+        <v>766</v>
+      </c>
+    </row>
+    <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" s="4">
         <v>738</v>
       </c>
       <c r="B122" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="D122">
+      <c r="D122" s="1">
         <v>481</v>
       </c>
-      <c r="E122">
-        <v>500</v>
-      </c>
-      <c r="F122">
-        <v>746</v>
-      </c>
-    </row>
-    <row r="123" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E122" s="1">
+        <v>602</v>
+      </c>
+      <c r="F122" s="1">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" s="4">
         <v>367</v>
       </c>
       <c r="B123" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="D123">
+      <c r="D123" s="1">
         <v>411</v>
       </c>
-      <c r="E123">
-        <v>834</v>
-      </c>
-      <c r="F123">
-        <v>475</v>
+      <c r="E123" s="1">
+        <v>673</v>
+      </c>
+      <c r="F123" s="1">
+        <v>783</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
@@ -38588,27 +38477,27 @@
         <v>579</v>
       </c>
       <c r="E124" s="3">
-        <v>698</v>
+        <v>434</v>
       </c>
       <c r="F124" s="3">
-        <v>607</v>
-      </c>
-    </row>
-    <row r="125" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" s="4">
         <v>797</v>
       </c>
       <c r="B125" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="D125">
+      <c r="D125" s="1">
         <v>662</v>
       </c>
-      <c r="E125">
-        <v>836</v>
-      </c>
-      <c r="F125">
-        <v>359</v>
+      <c r="E125" s="1">
+        <v>398</v>
+      </c>
+      <c r="F125" s="1">
+        <v>668</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
@@ -38621,79 +38510,79 @@
       <c r="D126" s="3">
         <v>495</v>
       </c>
-      <c r="E126" s="3">
-        <v>530</v>
-      </c>
-      <c r="F126" s="3">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="127" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E126" s="1">
+        <v>540</v>
+      </c>
+      <c r="F126" s="1">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" s="4">
         <v>502</v>
       </c>
       <c r="B127" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="D127">
+      <c r="D127" s="1">
         <v>723</v>
       </c>
-      <c r="E127">
-        <v>763</v>
-      </c>
-      <c r="F127">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="128" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E127" s="1">
+        <v>429</v>
+      </c>
+      <c r="F127" s="1">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" s="4">
         <v>481</v>
       </c>
       <c r="B128" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="D128">
+      <c r="D128" s="1">
         <v>791</v>
       </c>
-      <c r="E128">
-        <v>557</v>
-      </c>
-      <c r="F128">
-        <v>766</v>
-      </c>
-    </row>
-    <row r="129" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E128" s="1">
+        <v>580</v>
+      </c>
+      <c r="F128" s="1">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" s="4">
         <v>675</v>
       </c>
       <c r="B129" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="D129">
+      <c r="D129" s="1">
         <v>738</v>
       </c>
-      <c r="E129">
-        <v>602</v>
-      </c>
-      <c r="F129">
-        <v>556</v>
-      </c>
-    </row>
-    <row r="130" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E129" s="1">
+        <v>767</v>
+      </c>
+      <c r="F129" s="1">
+        <v>826</v>
+      </c>
+    </row>
+    <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" s="4">
         <v>774</v>
       </c>
       <c r="B130" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="D130">
+      <c r="D130" s="1">
         <v>668</v>
       </c>
-      <c r="E130">
-        <v>673</v>
-      </c>
-      <c r="F130">
-        <v>783</v>
+      <c r="E130" s="1">
+        <v>750</v>
+      </c>
+      <c r="F130" s="1">
+        <v>578</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
@@ -38707,112 +38596,112 @@
         <v>629</v>
       </c>
       <c r="E131" s="3">
-        <v>434</v>
+        <v>677</v>
       </c>
       <c r="F131" s="3">
-        <v>592</v>
-      </c>
-    </row>
-    <row r="132" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" s="4">
         <v>408</v>
       </c>
       <c r="B132" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="D132">
+      <c r="D132" s="1">
         <v>697</v>
       </c>
-      <c r="E132">
-        <v>398</v>
-      </c>
-      <c r="F132">
-        <v>668</v>
-      </c>
-    </row>
-    <row r="133" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E132" s="1">
+        <v>628</v>
+      </c>
+      <c r="F132" s="1">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" s="4">
         <v>527</v>
       </c>
       <c r="B133" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="D133">
+      <c r="D133" s="1">
         <v>357</v>
       </c>
-      <c r="E133">
-        <v>540</v>
-      </c>
-      <c r="F133">
-        <v>504</v>
-      </c>
-    </row>
-    <row r="134" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E133" s="3">
+        <v>704</v>
+      </c>
+      <c r="F133" s="3">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" s="4">
         <v>789</v>
       </c>
       <c r="B134" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="D134">
+      <c r="D134" s="1">
         <v>508</v>
       </c>
-      <c r="E134">
-        <v>429</v>
-      </c>
-      <c r="F134">
-        <v>592</v>
-      </c>
-    </row>
-    <row r="135" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E134" s="1">
+        <v>505</v>
+      </c>
+      <c r="F134" s="1">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" s="4">
         <v>502</v>
       </c>
       <c r="B135" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="D135">
+      <c r="D135" s="1">
         <v>430</v>
       </c>
-      <c r="E135">
-        <v>580</v>
-      </c>
-      <c r="F135">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="136" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E135" s="1">
+        <v>397</v>
+      </c>
+      <c r="F135" s="1">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" s="4">
         <v>511</v>
       </c>
       <c r="B136" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="D136">
+      <c r="D136" s="1">
         <v>845</v>
       </c>
-      <c r="E136">
-        <v>767</v>
-      </c>
-      <c r="F136">
-        <v>826</v>
-      </c>
-    </row>
-    <row r="137" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E136" s="3">
+        <v>361</v>
+      </c>
+      <c r="F136" s="3">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" s="4">
         <v>752</v>
       </c>
       <c r="B137" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="D137">
+      <c r="D137" s="1">
         <v>684</v>
       </c>
-      <c r="E137">
-        <v>750</v>
-      </c>
-      <c r="F137">
-        <v>578</v>
+      <c r="E137" s="1">
+        <v>837</v>
+      </c>
+      <c r="F137" s="1">
+        <v>567</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
@@ -38826,27 +38715,27 @@
         <v>513</v>
       </c>
       <c r="E138" s="3">
-        <v>677</v>
+        <v>636</v>
       </c>
       <c r="F138" s="3">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="139" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" s="4">
         <v>812</v>
       </c>
       <c r="B139" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="D139">
+      <c r="D139" s="1">
         <v>665</v>
       </c>
-      <c r="E139">
-        <v>628</v>
-      </c>
-      <c r="F139">
-        <v>466</v>
+      <c r="E139" s="3">
+        <v>440</v>
+      </c>
+      <c r="F139" s="3">
+        <v>350</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
@@ -38859,45 +38748,45 @@
       <c r="D140" s="3">
         <v>418</v>
       </c>
-      <c r="E140" s="3">
-        <v>704</v>
-      </c>
-      <c r="F140" s="3">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="141" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E140" s="1">
+        <v>640</v>
+      </c>
+      <c r="F140" s="1">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141" s="4">
         <v>485</v>
       </c>
       <c r="B141" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="D141">
+      <c r="D141" s="1">
         <v>451</v>
       </c>
-      <c r="E141">
-        <v>505</v>
-      </c>
-      <c r="F141">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="142" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E141" s="1">
+        <v>404</v>
+      </c>
+      <c r="F141" s="1">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A142" s="4">
         <v>787</v>
       </c>
       <c r="B142" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="D142">
+      <c r="D142" s="1">
         <v>713</v>
       </c>
-      <c r="E142">
-        <v>397</v>
-      </c>
-      <c r="F142">
-        <v>643</v>
+      <c r="E142" s="1">
+        <v>687</v>
+      </c>
+      <c r="F142" s="1">
+        <v>529</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
@@ -38911,27 +38800,27 @@
         <v>559</v>
       </c>
       <c r="E143" s="3">
-        <v>361</v>
+        <v>421</v>
       </c>
       <c r="F143" s="3">
-        <v>484</v>
-      </c>
-    </row>
-    <row r="144" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="144" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A144" s="4">
         <v>396</v>
       </c>
       <c r="B144" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="D144">
+      <c r="D144" s="1">
         <v>730</v>
       </c>
-      <c r="E144">
-        <v>837</v>
-      </c>
-      <c r="F144">
-        <v>567</v>
+      <c r="E144" s="3">
+        <v>715</v>
+      </c>
+      <c r="F144" s="3">
+        <v>759</v>
       </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
@@ -38944,11 +38833,11 @@
       <c r="D145" s="3">
         <v>507</v>
       </c>
-      <c r="E145" s="3">
-        <v>636</v>
-      </c>
-      <c r="F145" s="3">
-        <v>640</v>
+      <c r="E145" s="1">
+        <v>462</v>
+      </c>
+      <c r="F145" s="1">
+        <v>481</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
@@ -38962,61 +38851,61 @@
         <v>500</v>
       </c>
       <c r="E146" s="3">
-        <v>440</v>
+        <v>771</v>
       </c>
       <c r="F146" s="3">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="147" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="147" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A147" s="4">
         <v>767</v>
       </c>
       <c r="B147" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="D147">
+      <c r="D147" s="1">
         <v>473</v>
       </c>
-      <c r="E147">
-        <v>640</v>
-      </c>
-      <c r="F147">
-        <v>740</v>
-      </c>
-    </row>
-    <row r="148" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E147" s="1">
+        <v>787</v>
+      </c>
+      <c r="F147" s="1">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="148" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A148" s="4">
         <v>687</v>
       </c>
       <c r="B148" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="D148">
+      <c r="D148" s="1">
         <v>564</v>
       </c>
-      <c r="E148">
-        <v>404</v>
-      </c>
-      <c r="F148">
-        <v>485</v>
-      </c>
-    </row>
-    <row r="149" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E148" s="1">
+        <v>363</v>
+      </c>
+      <c r="F148" s="1">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="149" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A149" s="4">
         <v>507</v>
       </c>
       <c r="B149" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="D149">
+      <c r="D149" s="1">
         <v>409</v>
       </c>
-      <c r="E149">
-        <v>687</v>
-      </c>
-      <c r="F149">
-        <v>529</v>
+      <c r="E149" s="3">
+        <v>625</v>
+      </c>
+      <c r="F149" s="3">
+        <v>591</v>
       </c>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
@@ -39029,11 +38918,11 @@
       <c r="D150" s="3">
         <v>828</v>
       </c>
-      <c r="E150" s="3">
-        <v>421</v>
-      </c>
-      <c r="F150" s="3">
-        <v>657</v>
+      <c r="E150" s="1">
+        <v>614</v>
+      </c>
+      <c r="F150" s="1">
+        <v>579</v>
       </c>
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.25">
@@ -39046,28 +38935,28 @@
       <c r="D151" s="3">
         <v>515</v>
       </c>
-      <c r="E151" s="3">
-        <v>715</v>
-      </c>
-      <c r="F151" s="3">
-        <v>759</v>
-      </c>
-    </row>
-    <row r="152" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E151" s="1">
+        <v>702</v>
+      </c>
+      <c r="F151" s="1">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="152" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A152" s="4">
         <v>652</v>
       </c>
       <c r="B152" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="D152">
+      <c r="D152" s="1">
         <v>622</v>
       </c>
-      <c r="E152">
-        <v>462</v>
-      </c>
-      <c r="F152">
-        <v>481</v>
+      <c r="E152" s="3">
+        <v>603</v>
+      </c>
+      <c r="F152" s="3">
+        <v>807</v>
       </c>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.25">
@@ -39080,45 +38969,45 @@
       <c r="D153" s="3">
         <v>629</v>
       </c>
-      <c r="E153" s="3">
-        <v>771</v>
-      </c>
-      <c r="F153" s="3">
-        <v>671</v>
-      </c>
-    </row>
-    <row r="154" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E153" s="1">
+        <v>380</v>
+      </c>
+      <c r="F153" s="1">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="154" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A154" s="4">
         <v>638</v>
       </c>
       <c r="B154" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="D154">
+      <c r="D154" s="1">
         <v>643</v>
       </c>
-      <c r="E154">
-        <v>787</v>
-      </c>
-      <c r="F154">
-        <v>693</v>
-      </c>
-    </row>
-    <row r="155" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E154" s="3">
+        <v>605</v>
+      </c>
+      <c r="F154" s="3">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="155" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A155" s="4">
         <v>640</v>
       </c>
       <c r="B155" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="D155">
+      <c r="D155" s="1">
         <v>695</v>
       </c>
-      <c r="E155">
-        <v>363</v>
-      </c>
-      <c r="F155">
-        <v>549</v>
+      <c r="E155" s="1">
+        <v>610</v>
+      </c>
+      <c r="F155" s="1">
+        <v>600</v>
       </c>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.25">
@@ -39131,45 +39020,45 @@
       <c r="D156" s="3">
         <v>813</v>
       </c>
-      <c r="E156" s="3">
-        <v>625</v>
-      </c>
-      <c r="F156" s="3">
-        <v>591</v>
-      </c>
-    </row>
-    <row r="157" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E156" s="1">
+        <v>712</v>
+      </c>
+      <c r="F156" s="1">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="157" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A157" s="4">
         <v>437</v>
       </c>
       <c r="B157" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="D157">
+      <c r="D157" s="1">
         <v>451</v>
       </c>
-      <c r="E157">
-        <v>614</v>
-      </c>
-      <c r="F157">
-        <v>579</v>
-      </c>
-    </row>
-    <row r="158" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E157" s="1">
+        <v>424</v>
+      </c>
+      <c r="F157" s="1">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="158" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A158" s="4">
         <v>474</v>
       </c>
       <c r="B158" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="D158">
+      <c r="D158" s="1">
         <v>647</v>
       </c>
-      <c r="E158">
-        <v>702</v>
-      </c>
-      <c r="F158">
-        <v>524</v>
+      <c r="E158" s="3">
+        <v>666</v>
+      </c>
+      <c r="F158" s="3">
+        <v>638</v>
       </c>
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.25">
@@ -39183,24 +39072,25 @@
         <v>393</v>
       </c>
       <c r="E159" s="3">
-        <v>603</v>
+        <v>559</v>
       </c>
       <c r="F159" s="3">
-        <v>807</v>
-      </c>
-    </row>
-    <row r="160" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="160" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A160" s="4">
         <v>524</v>
       </c>
       <c r="B160" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="E160">
-        <v>380</v>
-      </c>
-      <c r="F160">
-        <v>450</v>
+      <c r="D160" s="1"/>
+      <c r="E160" s="1">
+        <v>646</v>
+      </c>
+      <c r="F160" s="1">
+        <v>605</v>
       </c>
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.25">
@@ -39211,53 +39101,56 @@
         <v>24</v>
       </c>
       <c r="D161" s="3"/>
-      <c r="E161" s="3">
-        <v>605</v>
-      </c>
-      <c r="F161" s="3">
-        <v>732</v>
-      </c>
-    </row>
-    <row r="162" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E161" s="1">
+        <v>840</v>
+      </c>
+      <c r="F161" s="1">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="162" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A162" s="4">
         <v>713</v>
       </c>
       <c r="B162" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="E162">
-        <v>610</v>
-      </c>
-      <c r="F162">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="163" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D162" s="1"/>
+      <c r="E162" s="3">
+        <v>575</v>
+      </c>
+      <c r="F162" s="3">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="163" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A163" s="4">
         <v>402</v>
       </c>
       <c r="B163" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="E163">
-        <v>712</v>
-      </c>
-      <c r="F163">
-        <v>608</v>
-      </c>
-    </row>
-    <row r="164" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D163" s="1"/>
+      <c r="E163" s="1">
+        <v>444</v>
+      </c>
+      <c r="F163" s="1">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="164" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A164" s="4">
         <v>839</v>
       </c>
       <c r="B164" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="E164">
-        <v>424</v>
-      </c>
-      <c r="F164">
-        <v>511</v>
+      <c r="D164" s="1"/>
+      <c r="E164" s="1">
+        <v>588</v>
+      </c>
+      <c r="F164" s="1">
+        <v>569</v>
       </c>
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.25">
@@ -39268,11 +39161,11 @@
         <v>24</v>
       </c>
       <c r="D165" s="3"/>
-      <c r="E165" s="3">
-        <v>666</v>
-      </c>
-      <c r="F165" s="3">
-        <v>638</v>
+      <c r="E165" s="1">
+        <v>566</v>
+      </c>
+      <c r="F165" s="1">
+        <v>720</v>
       </c>
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.25">
@@ -39283,39 +39176,41 @@
         <v>24</v>
       </c>
       <c r="D166" s="3"/>
-      <c r="E166" s="3">
-        <v>559</v>
-      </c>
-      <c r="F166" s="3">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="167" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E166" s="1">
+        <v>705</v>
+      </c>
+      <c r="F166" s="1">
+        <v>774</v>
+      </c>
+    </row>
+    <row r="167" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A167" s="4">
         <v>682</v>
       </c>
       <c r="B167" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="E167">
-        <v>646</v>
-      </c>
-      <c r="F167">
-        <v>605</v>
-      </c>
-    </row>
-    <row r="168" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D167" s="1"/>
+      <c r="E167" s="3">
+        <v>517</v>
+      </c>
+      <c r="F167" s="3">
+        <v>790</v>
+      </c>
+    </row>
+    <row r="168" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A168" s="4">
         <v>724</v>
       </c>
       <c r="B168" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="E168">
-        <v>840</v>
-      </c>
-      <c r="F168">
-        <v>580</v>
+      <c r="D168" s="1"/>
+      <c r="E168" s="3">
+        <v>507</v>
+      </c>
+      <c r="F168" s="3">
+        <v>659</v>
       </c>
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.25">
@@ -39326,67 +39221,71 @@
         <v>24</v>
       </c>
       <c r="D169" s="3"/>
-      <c r="E169" s="3">
-        <v>575</v>
-      </c>
-      <c r="F169" s="3">
-        <v>534</v>
-      </c>
-    </row>
-    <row r="170" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E169" s="1">
+        <v>415</v>
+      </c>
+      <c r="F169" s="1">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="170" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A170" s="4">
         <v>496</v>
       </c>
       <c r="B170" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="E170">
-        <v>444</v>
-      </c>
-      <c r="F170">
-        <v>820</v>
-      </c>
-    </row>
-    <row r="171" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D170" s="1"/>
+      <c r="E170" s="1">
+        <v>437</v>
+      </c>
+      <c r="F170" s="1">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="171" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A171" s="4">
         <v>610</v>
       </c>
       <c r="B171" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="E171">
-        <v>588</v>
-      </c>
-      <c r="F171">
-        <v>569</v>
-      </c>
-    </row>
-    <row r="172" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D171" s="1"/>
+      <c r="E171" s="3">
+        <v>760</v>
+      </c>
+      <c r="F171" s="3">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="172" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A172" s="4">
         <v>613</v>
       </c>
       <c r="B172" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="E172">
-        <v>566</v>
-      </c>
-      <c r="F172">
-        <v>720</v>
-      </c>
-    </row>
-    <row r="173" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D172" s="1"/>
+      <c r="E172" s="3">
+        <v>567</v>
+      </c>
+      <c r="F172" s="3">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="173" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A173" s="4">
         <v>481</v>
       </c>
       <c r="B173" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="E173">
-        <v>705</v>
-      </c>
-      <c r="F173">
-        <v>774</v>
+      <c r="D173" s="1"/>
+      <c r="E173" s="1">
+        <v>566</v>
+      </c>
+      <c r="F173" s="1">
+        <v>466</v>
       </c>
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.25">
@@ -39397,11 +39296,9 @@
         <v>24</v>
       </c>
       <c r="D174" s="3"/>
-      <c r="E174" s="3">
-        <v>517</v>
-      </c>
-      <c r="F174" s="3">
-        <v>790</v>
+      <c r="E174" s="1"/>
+      <c r="F174" s="1">
+        <v>397</v>
       </c>
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.25">
@@ -39411,98 +39308,61 @@
       <c r="B175" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="D175" s="3"/>
-      <c r="E175" s="3">
-        <v>507</v>
-      </c>
-      <c r="F175" s="3">
-        <v>659</v>
-      </c>
-    </row>
-    <row r="176" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D175" s="20"/>
+    </row>
+    <row r="176" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A176" s="4">
         <v>643</v>
       </c>
       <c r="B176" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="E176">
-        <v>415</v>
-      </c>
-      <c r="F176">
-        <v>739</v>
-      </c>
-    </row>
-    <row r="177" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D176" s="21"/>
+    </row>
+    <row r="177" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A177" s="4">
         <v>466</v>
       </c>
       <c r="B177" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="E177">
-        <v>437</v>
-      </c>
-      <c r="F177">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="178" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D177" s="21"/>
+    </row>
+    <row r="178" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A178" s="4">
         <v>843</v>
       </c>
       <c r="B178" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="D178" s="3"/>
-      <c r="E178" s="3">
-        <v>760</v>
-      </c>
-      <c r="F178" s="3">
-        <v>538</v>
-      </c>
-    </row>
-    <row r="179" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D178" s="20"/>
+    </row>
+    <row r="179" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A179" s="4">
         <v>398</v>
       </c>
       <c r="B179" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="D179" s="3"/>
-      <c r="E179" s="3">
-        <v>567</v>
-      </c>
-      <c r="F179" s="3">
-        <v>638</v>
-      </c>
-    </row>
-    <row r="180" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D179" s="20"/>
+    </row>
+    <row r="180" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A180" s="4">
         <v>459</v>
       </c>
       <c r="B180" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="E180">
-        <v>566</v>
-      </c>
-      <c r="F180">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="181" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="181" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A181" s="4">
         <v>816</v>
       </c>
       <c r="B181" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="F181">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="182" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="182" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A182" s="4">
         <v>529</v>
       </c>
@@ -39510,7 +39370,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="183" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A183" s="4">
         <v>399</v>
       </c>
@@ -39518,7 +39378,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="184" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A184" s="4">
         <v>421</v>
       </c>
@@ -39526,7 +39386,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="185" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A185" s="4">
         <v>696</v>
       </c>
@@ -39534,7 +39394,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="186" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A186" s="4">
         <v>783</v>
       </c>
@@ -39542,7 +39402,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="187" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A187" s="4">
         <v>844</v>
       </c>
@@ -39550,7 +39410,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="188" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A188" s="4">
         <v>635</v>
       </c>
@@ -39558,7 +39418,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="189" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A189" s="4">
         <v>353</v>
       </c>
@@ -39566,7 +39426,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="190" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A190" s="4">
         <v>424</v>
       </c>
@@ -39574,7 +39434,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="191" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A191" s="4">
         <v>434</v>
       </c>
@@ -39582,7 +39442,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="192" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A192" s="4">
         <v>840</v>
       </c>
@@ -39590,7 +39450,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="193" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A193" s="4">
         <v>671</v>
       </c>
@@ -39614,7 +39474,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="196" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A196" s="4">
         <v>558</v>
       </c>
@@ -39622,7 +39482,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="197" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A197" s="4">
         <v>392</v>
       </c>
@@ -39630,7 +39490,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="198" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A198" s="4">
         <v>848</v>
       </c>
@@ -39638,7 +39498,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="199" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A199" s="4">
         <v>378</v>
       </c>
@@ -39654,7 +39514,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="201" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A201" s="4">
         <v>693</v>
       </c>
@@ -39662,7 +39522,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="202" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A202" s="4">
         <v>530</v>
       </c>
@@ -39678,7 +39538,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="204" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A204" s="4">
         <v>800</v>
       </c>
@@ -39686,7 +39546,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="205" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A205" s="4">
         <v>452</v>
       </c>
@@ -39702,7 +39562,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="207" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A207" s="4">
         <v>608</v>
       </c>
@@ -39718,7 +39578,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="209" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A209" s="4">
         <v>714</v>
       </c>
@@ -39734,7 +39594,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="211" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A211" s="4">
         <v>695</v>
       </c>
@@ -39742,7 +39602,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="212" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A212" s="4">
         <v>730</v>
       </c>
@@ -39750,7 +39610,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="213" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A213" s="4">
         <v>723</v>
       </c>
@@ -39766,7 +39626,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="215" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A215" s="4">
         <v>440</v>
       </c>
@@ -39774,7 +39634,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="216" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A216" s="4">
         <v>418</v>
       </c>
@@ -39782,7 +39642,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="217" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A217" s="4">
         <v>455</v>
       </c>
@@ -39790,7 +39650,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="218" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A218" s="4">
         <v>360</v>
       </c>
@@ -39798,7 +39658,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="219" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A219" s="4">
         <v>362</v>
       </c>
@@ -39814,7 +39674,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="221" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A221" s="4">
         <v>575</v>
       </c>
@@ -39830,7 +39690,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="223" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A223" s="4">
         <v>517</v>
       </c>
@@ -39838,7 +39698,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="224" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A224" s="4">
         <v>766</v>
       </c>
@@ -39854,7 +39714,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="226" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A226" s="4">
         <v>639</v>
       </c>
@@ -39870,7 +39730,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="228" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A228" s="4">
         <v>449</v>
       </c>
@@ -39878,7 +39738,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="229" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A229" s="4">
         <v>567</v>
       </c>
@@ -39886,7 +39746,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="230" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A230" s="4">
         <v>656</v>
       </c>
@@ -39894,7 +39754,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="231" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A231" s="4">
         <v>694</v>
       </c>
@@ -39902,7 +39762,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="232" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A232" s="4">
         <v>560</v>
       </c>
@@ -39910,7 +39770,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="233" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A233" s="4">
         <v>626</v>
       </c>
@@ -39918,7 +39778,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="234" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A234" s="4">
         <v>572</v>
       </c>
@@ -39926,7 +39786,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="235" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A235" s="4">
         <v>506</v>
       </c>
@@ -39950,7 +39810,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="238" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A238" s="4">
         <v>759</v>
       </c>
@@ -39974,7 +39834,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="241" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A241" s="4">
         <v>584</v>
       </c>
@@ -39990,7 +39850,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="243" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A243" s="4">
         <v>634</v>
       </c>
@@ -39998,7 +39858,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="244" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A244" s="4">
         <v>502</v>
       </c>
@@ -40006,7 +39866,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="245" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A245" s="4">
         <v>496</v>
       </c>
@@ -40022,7 +39882,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="247" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A247" s="4">
         <v>522</v>
       </c>
@@ -40030,7 +39890,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="248" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A248" s="4">
         <v>561</v>
       </c>
@@ -40038,7 +39898,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="249" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A249" s="4">
         <v>651</v>
       </c>
@@ -40046,7 +39906,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="250" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A250" s="4">
         <v>660</v>
       </c>
@@ -40054,7 +39914,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="251" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A251" s="4">
         <v>350</v>
       </c>
@@ -40070,7 +39930,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="253" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A253" s="4">
         <v>545</v>
       </c>
@@ -40086,7 +39946,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="255" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A255" s="4">
         <v>569</v>
       </c>
@@ -40094,7 +39954,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="256" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A256" s="4">
         <v>705</v>
       </c>
@@ -40110,7 +39970,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="258" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A258" s="4">
         <v>804</v>
       </c>
@@ -40126,7 +39986,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="260" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A260" s="4">
         <v>512</v>
       </c>
@@ -40134,7 +39994,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="261" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A261" s="4">
         <v>400</v>
       </c>
@@ -40142,7 +40002,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="262" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A262" s="4">
         <v>592</v>
       </c>
@@ -40150,7 +40010,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="263" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A263" s="4">
         <v>708</v>
       </c>
@@ -40158,7 +40018,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="264" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A264" s="4">
         <v>370</v>
       </c>
@@ -40166,7 +40026,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="265" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A265" s="4">
         <v>521</v>
       </c>
@@ -40190,7 +40050,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="268" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A268" s="4">
         <v>834</v>
       </c>
@@ -40206,7 +40066,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="270" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A270" s="4">
         <v>455</v>
       </c>
@@ -40214,7 +40074,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="271" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A271" s="4">
         <v>544</v>
       </c>
@@ -40222,7 +40082,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="272" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A272" s="4">
         <v>575</v>
       </c>
@@ -40230,7 +40090,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="273" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A273" s="4">
         <v>490</v>
       </c>
@@ -40294,7 +40154,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="281" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A281" s="4">
         <v>607</v>
       </c>
@@ -40326,7 +40186,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="285" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A285" s="4">
         <v>612</v>
       </c>
@@ -40342,7 +40202,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="287" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A287" s="4">
         <v>772</v>
       </c>
@@ -40350,7 +40210,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="288" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A288" s="4">
         <v>681</v>
       </c>
@@ -40358,7 +40218,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="289" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A289" s="4">
         <v>720</v>
       </c>
@@ -40366,7 +40226,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="290" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A290" s="4">
         <v>691</v>
       </c>
@@ -40382,7 +40242,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="292" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A292" s="4">
         <v>720</v>
       </c>
@@ -40398,7 +40258,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="294" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A294" s="4">
         <v>657</v>
       </c>
@@ -40406,7 +40266,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="295" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A295" s="4">
         <v>608</v>
       </c>
@@ -40430,7 +40290,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="298" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A298" s="4">
         <v>359</v>
       </c>
@@ -40454,7 +40314,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="301" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A301" s="4">
         <v>739</v>
       </c>
@@ -40462,7 +40322,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="302" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A302" s="4">
         <v>466</v>
       </c>
@@ -40470,7 +40330,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="303" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A303" s="4">
         <v>531</v>
       </c>
@@ -40478,7 +40338,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="304" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A304" s="4">
         <v>585</v>
       </c>
@@ -40486,7 +40346,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="305" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A305" s="4">
         <v>543</v>
       </c>
@@ -40510,7 +40370,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="308" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A308" s="4">
         <v>412</v>
       </c>
@@ -40518,7 +40378,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="309" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A309" s="4">
         <v>682</v>
       </c>
@@ -40526,7 +40386,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="310" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A310" s="4">
         <v>397</v>
       </c>
@@ -40534,7 +40394,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="311" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A311" s="4">
         <v>426</v>
       </c>
@@ -40542,7 +40402,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="312" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A312" s="4">
         <v>499</v>
       </c>
@@ -40558,7 +40418,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="314" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A314" s="4">
         <v>624</v>
       </c>
@@ -40574,7 +40434,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="316" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A316" s="4">
         <v>363</v>
       </c>
@@ -40598,7 +40458,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="319" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A319" s="4">
         <v>586</v>
       </c>
@@ -40614,7 +40474,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="321" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A321" s="4">
         <v>563</v>
       </c>
@@ -40622,7 +40482,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="322" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A322" s="4">
         <v>356</v>
       </c>
@@ -40630,7 +40490,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="323" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A323" s="4">
         <v>450</v>
       </c>
@@ -40646,7 +40506,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="325" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A325" s="4">
         <v>390</v>
       </c>
@@ -40654,7 +40514,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="326" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A326" s="4">
         <v>760</v>
       </c>
@@ -40678,7 +40538,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="329" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A329" s="4">
         <v>493</v>
       </c>
@@ -40686,7 +40546,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="330" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A330" s="4">
         <v>797</v>
       </c>
@@ -40694,7 +40554,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="331" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A331" s="4">
         <v>835</v>
       </c>
@@ -40702,7 +40562,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="332" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A332" s="4">
         <v>387</v>
       </c>
@@ -40710,7 +40570,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="333" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A333" s="4">
         <v>409</v>
       </c>
@@ -40734,7 +40594,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="336" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A336" s="4">
         <v>702</v>
       </c>
@@ -40742,7 +40602,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="337" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A337" s="4">
         <v>846</v>
       </c>
@@ -40750,7 +40610,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="338" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A338" s="4">
         <v>558</v>
       </c>
@@ -40758,7 +40618,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="339" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A339" s="4">
         <v>638</v>
       </c>
@@ -40766,7 +40626,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="340" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A340" s="4">
         <v>412</v>
       </c>
@@ -40774,7 +40634,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="341" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A341" s="4">
         <v>744</v>
       </c>
@@ -40782,7 +40642,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="342" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A342" s="4">
         <v>746</v>
       </c>
@@ -40790,7 +40650,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="343" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A343" s="4">
         <v>443</v>
       </c>
@@ -40806,7 +40666,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="345" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A345" s="4">
         <v>763</v>
       </c>
@@ -40838,7 +40698,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="349" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A349" s="4">
         <v>753</v>
       </c>
@@ -40846,7 +40706,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="350" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A350" s="4">
         <v>739</v>
       </c>
@@ -40854,7 +40714,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="351" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A351" s="4">
         <v>642</v>
       </c>
@@ -40862,7 +40722,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="352" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A352" s="4">
         <v>433</v>
       </c>
@@ -40870,7 +40730,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="353" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A353" s="4">
         <v>477</v>
       </c>
@@ -40886,7 +40746,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="355" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A355" s="4">
         <v>611</v>
       </c>
@@ -40902,7 +40762,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="357" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A357" s="4">
         <v>810</v>
       </c>
@@ -40910,7 +40770,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="358" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A358" s="4">
         <v>504</v>
       </c>
@@ -40918,7 +40778,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="359" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A359" s="4">
         <v>591</v>
       </c>
@@ -40926,7 +40786,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="360" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A360" s="4">
         <v>433</v>
       </c>
@@ -40934,7 +40794,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="361" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A361" s="4">
         <v>746</v>
       </c>
@@ -40950,7 +40810,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="363" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A363" s="4">
         <v>485</v>
       </c>
@@ -40966,7 +40826,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="365" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A365" s="4">
         <v>430</v>
       </c>
@@ -40982,7 +40842,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="367" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A367" s="4">
         <v>350</v>
       </c>
@@ -40990,7 +40850,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="368" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A368" s="4">
         <v>565</v>
       </c>
@@ -41006,7 +40866,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="370" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A370" s="4">
         <v>680</v>
       </c>
@@ -41022,7 +40882,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="372" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A372" s="4">
         <v>481</v>
       </c>
@@ -41030,7 +40890,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="373" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A373" s="4">
         <v>411</v>
       </c>
@@ -41046,7 +40906,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="375" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A375" s="4">
         <v>494</v>
       </c>
@@ -41054,7 +40914,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="376" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A376" s="4">
         <v>718</v>
       </c>
@@ -41062,7 +40922,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="377" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A377" s="4">
         <v>807</v>
       </c>
@@ -41078,7 +40938,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="379" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A379" s="4">
         <v>466</v>
       </c>
@@ -41086,7 +40946,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="380" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A380" s="4">
         <v>579</v>
       </c>
@@ -41094,7 +40954,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="381" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A381" s="4">
         <v>605</v>
       </c>
@@ -41102,7 +40962,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="382" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A382" s="4">
         <v>662</v>
       </c>
@@ -41110,7 +40970,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="383" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A383" s="4">
         <v>668</v>
       </c>
@@ -41118,7 +40978,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="384" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A384" s="4">
         <v>790</v>
       </c>
@@ -41134,7 +40994,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="386" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A386" s="4">
         <v>495</v>
       </c>
@@ -41142,7 +41002,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="387" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A387" s="4">
         <v>723</v>
       </c>
@@ -41150,7 +41010,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="388" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A388" s="4">
         <v>791</v>
       </c>
@@ -41158,7 +41018,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="389" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A389" s="4">
         <v>359</v>
       </c>
@@ -41166,7 +41026,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="390" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A390" s="4">
         <v>842</v>
       </c>
@@ -41198,7 +41058,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="394" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A394" s="4">
         <v>556</v>
       </c>
@@ -41214,7 +41074,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="396" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A396" s="4">
         <v>738</v>
       </c>
@@ -41230,7 +41090,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="398" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A398" s="4">
         <v>578</v>
       </c>
@@ -41246,7 +41106,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="400" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A400" s="4">
         <v>668</v>
       </c>
@@ -41254,7 +41114,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="401" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A401" s="4">
         <v>629</v>
       </c>
@@ -41262,7 +41122,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="402" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A402" s="4">
         <v>697</v>
       </c>
@@ -41270,7 +41130,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="403" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A403" s="4">
         <v>716</v>
       </c>
@@ -41278,7 +41138,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="404" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A404" s="4">
         <v>357</v>
       </c>
@@ -41302,7 +41162,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="407" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A407" s="4">
         <v>508</v>
       </c>
@@ -41310,7 +41170,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="408" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A408" s="4">
         <v>596</v>
       </c>
@@ -41318,7 +41178,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="409" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A409" s="4">
         <v>430</v>
       </c>
@@ -41342,7 +41202,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="412" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A412" s="4">
         <v>845</v>
       </c>
@@ -41350,7 +41210,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="413" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A413" s="4">
         <v>464</v>
       </c>
@@ -41366,7 +41226,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="415" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A415" s="4">
         <v>821</v>
       </c>
@@ -41374,7 +41234,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="416" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A416" s="4">
         <v>684</v>
       </c>
@@ -41430,7 +41290,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="423" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A423" s="4">
         <v>513</v>
       </c>
@@ -41454,7 +41314,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="426" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A426" s="4">
         <v>665</v>
       </c>
@@ -41478,7 +41338,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="429" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A429" s="4">
         <v>418</v>
       </c>
@@ -41502,7 +41362,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="432" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A432" s="4">
         <v>451</v>
       </c>
@@ -41518,7 +41378,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="434" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A434" s="4">
         <v>713</v>
       </c>
@@ -41542,7 +41402,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="437" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A437" s="4">
         <v>559</v>
       </c>
@@ -41550,7 +41410,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="438" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A438" s="4">
         <v>547</v>
       </c>
@@ -41558,7 +41418,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="439" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A439" s="4">
         <v>730</v>
       </c>
@@ -41566,7 +41426,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="440" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A440" s="4">
         <v>450</v>
       </c>
@@ -41574,7 +41434,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="441" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A441" s="4">
         <v>735</v>
       </c>
@@ -41590,7 +41450,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="443" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A443" s="4">
         <v>507</v>
       </c>
@@ -41598,7 +41458,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="444" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A444" s="4">
         <v>739</v>
       </c>
@@ -41606,7 +41466,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="445" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A445" s="4">
         <v>814</v>
       </c>
@@ -41614,7 +41474,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="446" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A446" s="4">
         <v>580</v>
       </c>
@@ -41622,7 +41482,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="447" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A447" s="4">
         <v>774</v>
       </c>
@@ -41630,7 +41490,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="448" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A448" s="4">
         <v>500</v>
       </c>
@@ -41654,7 +41514,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="451" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A451" s="4">
         <v>369</v>
       </c>
@@ -41670,7 +41530,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="453" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A453" s="4">
         <v>498</v>
       </c>
@@ -41694,7 +41554,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="456" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A456" s="4">
         <v>473</v>
       </c>
@@ -41702,7 +41562,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="457" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A457" s="4">
         <v>801</v>
       </c>
@@ -41710,7 +41570,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="458" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A458" s="4">
         <v>564</v>
       </c>
@@ -41726,7 +41586,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="460" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A460" s="4">
         <v>579</v>
       </c>
@@ -41734,7 +41594,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="461" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A461" s="4">
         <v>600</v>
       </c>
@@ -41742,7 +41602,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="462" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A462" s="4">
         <v>443</v>
       </c>
@@ -41750,7 +41610,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="463" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A463" s="4">
         <v>519</v>
       </c>
@@ -41758,7 +41618,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="464" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A464" s="4">
         <v>390</v>
       </c>
@@ -41766,7 +41626,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="465" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A465" s="4">
         <v>538</v>
       </c>
@@ -41782,7 +41642,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="467" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A467" s="4">
         <v>529</v>
       </c>
@@ -41798,7 +41658,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="469" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A469" s="4">
         <v>409</v>
       </c>
@@ -41814,7 +41674,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="471" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A471" s="4">
         <v>828</v>
       </c>
@@ -41822,7 +41682,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="472" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A472" s="4">
         <v>379</v>
       </c>
@@ -41854,7 +41714,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="476" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A476" s="4">
         <v>515</v>
       </c>
@@ -41862,7 +41722,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="477" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A477" s="4">
         <v>732</v>
       </c>
@@ -41878,7 +41738,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="479" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A479" s="4">
         <v>622</v>
       </c>
@@ -41918,7 +41778,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="484" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A484" s="4">
         <v>629</v>
       </c>
@@ -41926,7 +41786,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="485" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="485" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A485" s="4">
         <v>550</v>
       </c>
@@ -41934,7 +41794,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="486" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A486" s="4">
         <v>734</v>
       </c>
@@ -41950,7 +41810,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="488" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A488" s="4">
         <v>643</v>
       </c>
@@ -41958,7 +41818,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="489" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A489" s="4">
         <v>717</v>
       </c>
@@ -41966,7 +41826,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="490" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="490" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A490" s="4">
         <v>797</v>
       </c>
@@ -41990,7 +41850,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="493" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="493" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A493" s="4">
         <v>695</v>
       </c>
@@ -41998,7 +41858,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="494" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="494" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A494" s="4">
         <v>484</v>
       </c>
@@ -42014,7 +41874,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="496" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A496" s="4">
         <v>813</v>
       </c>
@@ -42022,7 +41882,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="497" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A497" s="4">
         <v>451</v>
       </c>
@@ -42030,7 +41890,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="498" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="498" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A498" s="4">
         <v>647</v>
       </c>
@@ -42038,7 +41898,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="499" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="499" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A499" s="4">
         <v>751</v>
       </c>
@@ -42046,7 +41906,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="500" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="500" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A500" s="4">
         <v>814</v>
       </c>
@@ -42054,7 +41914,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="501" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="501" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A501" s="4">
         <v>718</v>
       </c>
@@ -42062,7 +41922,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="502" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="502" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A502" s="4">
         <v>393</v>
       </c>
@@ -42071,13 +41931,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:B502" xr:uid="{3C579A25-9064-487F-AB78-040E4F8F7CDA}">
-    <filterColumn colId="1">
-      <filters>
-        <filter val="France"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A2:B502" xr:uid="{3C579A25-9064-487F-AB78-040E4F8F7CDA}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>